--- a/data/MEYSU (TRY).xlsx
+++ b/data/MEYSU (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,22 +451,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>697646099</v>
+        <v>429861163</v>
       </c>
       <c r="C3">
-        <v>59482591</v>
+        <v>746574820.7624693</v>
       </c>
       <c r="D3">
-        <v>90353769.37420186</v>
+        <v>63653574</v>
       </c>
       <c r="E3">
-        <v>77375192.0914661</v>
+        <v>96690641.96366738</v>
       </c>
       <c r="F3">
-        <v>262943997.43199435</v>
+        <v>82801824.95100275</v>
       </c>
       <c r="G3">
-        <v>132497984.40131028</v>
+        <v>281385315.6130933</v>
+      </c>
+      <c r="H3">
+        <v>141790599.98699522</v>
       </c>
     </row>
     <row r="4">
@@ -474,6 +481,9 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
+      <c r="B5">
+        <v>62270681</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -485,22 +495,25 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>819396658</v>
+        <v>964741570</v>
       </c>
       <c r="C7">
-        <v>809461989</v>
+        <v>876864235.2570746</v>
       </c>
       <c r="D7">
-        <v>893713074.5213796</v>
+        <v>866222340</v>
       </c>
       <c r="E7">
-        <v>566023162.3836795</v>
+        <v>956392760.4271952</v>
       </c>
       <c r="F7">
-        <v>558140569.6422449</v>
+        <v>605720639.1746793</v>
       </c>
       <c r="G7">
-        <v>639404709.5310613</v>
+        <v>597285208.558045</v>
+      </c>
+      <c r="H7">
+        <v>684248728.8283838</v>
       </c>
     </row>
     <row r="8">
@@ -518,22 +531,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>775184</v>
+        <v>56280357</v>
       </c>
       <c r="C10">
-        <v>129432875</v>
+        <v>829550.7660509888</v>
       </c>
       <c r="D10">
-        <v>375741897.9922666</v>
+        <v>138508849</v>
       </c>
       <c r="E10">
-        <v>105495378.0479016</v>
+        <v>402094185.7893574</v>
       </c>
       <c r="F10">
-        <v>40717096.49344563</v>
+        <v>112894192.4426658</v>
       </c>
       <c r="G10">
-        <v>500387882.5556512</v>
+        <v>43572749.937446915</v>
+      </c>
+      <c r="H10">
+        <v>535482093.66637164</v>
       </c>
     </row>
     <row r="11">
@@ -556,22 +572,25 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>1053771356</v>
+        <v>1090523964</v>
       </c>
       <c r="C14">
-        <v>957297356</v>
+        <v>1127676571.7718494</v>
       </c>
       <c r="D14">
-        <v>808129684.699378</v>
+        <v>1024424085</v>
       </c>
       <c r="E14">
-        <v>890561468.6544864</v>
+        <v>864807063.8853654</v>
       </c>
       <c r="F14">
-        <v>873687411.0850673</v>
+        <v>953020119.7881056</v>
       </c>
       <c r="G14">
-        <v>890842845.5612642</v>
+        <v>934962616.8170689</v>
+      </c>
+      <c r="H14">
+        <v>953321230.7869995</v>
       </c>
     </row>
     <row r="15">
@@ -589,22 +608,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>101470445</v>
+        <v>37677213</v>
       </c>
       <c r="C17">
-        <v>82924086</v>
+        <v>108586974.68121727</v>
       </c>
       <c r="D17">
-        <v>60298820.116915435</v>
+        <v>88738813</v>
       </c>
       <c r="E17">
-        <v>23285249.526761092</v>
+        <v>64527818.45337103</v>
       </c>
       <c r="F17">
-        <v>21326074.411556117</v>
+        <v>24918337.559357636</v>
       </c>
       <c r="G17">
-        <v>39170772.5581637</v>
+        <v>22821757.627823547</v>
+      </c>
+      <c r="H17">
+        <v>41917976.0965574</v>
       </c>
     </row>
     <row r="18">
@@ -616,8 +638,8 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
-      <c r="D19">
-        <v>329201.48453620495</v>
+      <c r="E19">
+        <v>352289.70629183727</v>
       </c>
     </row>
     <row r="20">
@@ -630,22 +652,25 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>99832272</v>
+        <v>94905934</v>
       </c>
       <c r="C21">
-        <v>80128478</v>
+        <v>106833910.03195459</v>
       </c>
       <c r="D21">
-        <v>63632222.56877187</v>
+        <v>85005297</v>
       </c>
       <c r="E21">
-        <v>83512339.35442689</v>
+        <v>68095005.80178605</v>
       </c>
       <c r="F21">
-        <v>62164887.7434679</v>
+        <v>89369394.99031839</v>
       </c>
       <c r="G21">
-        <v>93661653.23912902</v>
+        <v>66524760.8942748</v>
+      </c>
+      <c r="H21">
+        <v>100230521.0042023</v>
       </c>
     </row>
     <row r="22">
@@ -663,22 +688,25 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>2772892014</v>
+        <v>2736260882</v>
       </c>
       <c r="C24">
-        <v>2118727375</v>
+        <v>2967366063.270616</v>
       </c>
       <c r="D24">
-        <v>2292198670.7574496</v>
+        <v>2266552958</v>
       </c>
       <c r="E24">
-        <v>1746252790.0587215</v>
+        <v>2452959766.0270343</v>
       </c>
       <c r="F24">
-        <v>1818980036.8077762</v>
+        <v>1868724508.9061294</v>
       </c>
       <c r="G24">
-        <v>2295965847.8465796</v>
+        <v>1946552409.4477525</v>
+      </c>
+      <c r="H24">
+        <v>2456991150.3695097</v>
       </c>
     </row>
     <row r="25">
@@ -694,19 +722,22 @@
         <v>273</v>
       </c>
       <c r="C26">
-        <v>300</v>
+        <v>292.1465860130239</v>
       </c>
       <c r="D26">
-        <v>313.49897541592173</v>
+        <v>321</v>
       </c>
       <c r="E26">
-        <v>391.75024687879744</v>
+        <v>335.48591716608956</v>
       </c>
       <c r="F26">
-        <v>566.1355123811335</v>
+        <v>419.22526445201447</v>
       </c>
       <c r="G26">
-        <v>932.4584909806903</v>
+        <v>605.8408687285062</v>
+      </c>
+      <c r="H26">
+        <v>997.85554849401</v>
       </c>
     </row>
     <row r="27">
@@ -732,19 +763,22 @@
         <v>268570</v>
       </c>
       <c r="C30">
-        <v>327974</v>
+        <v>287405.8923279042</v>
       </c>
       <c r="D30">
-        <v>308531.2224208694</v>
+        <v>350972</v>
       </c>
       <c r="E30">
-        <v>178586.3927407673</v>
+        <v>330169.7557094577</v>
       </c>
       <c r="F30">
-        <v>332423.7487304067</v>
+        <v>191111.3734344185</v>
       </c>
       <c r="G30">
-        <v>207617.85442590623</v>
+        <v>355737.96081040154</v>
+      </c>
+      <c r="H30">
+        <v>222178.92808013735</v>
       </c>
     </row>
     <row r="31">
@@ -781,8 +815,8 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
-      <c r="G37">
-        <v>12846006.362560213</v>
+      <c r="H37">
+        <v>13746948.361624725</v>
       </c>
     </row>
     <row r="38">
@@ -795,22 +829,25 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>3879540118</v>
+        <v>4317205729</v>
       </c>
       <c r="C39">
-        <v>3807809553</v>
+        <v>4151627841.663971</v>
       </c>
       <c r="D39">
-        <v>3449268403.8236947</v>
+        <v>4074817284</v>
       </c>
       <c r="E39">
-        <v>2672032379.220671</v>
+        <v>3691179444.7607503</v>
       </c>
       <c r="F39">
-        <v>2300908673.6538687</v>
+        <v>2859432737.383065</v>
       </c>
       <c r="G39">
-        <v>1657990143.5847733</v>
+        <v>2462280636.3946257</v>
+      </c>
+      <c r="H39">
+        <v>1774271648.686941</v>
       </c>
     </row>
     <row r="40">
@@ -818,42 +855,48 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
-        <v>916651</v>
+        <v>8853950</v>
       </c>
       <c r="C40">
-        <v>916651</v>
+        <v>980939.4147085142</v>
       </c>
       <c r="D40">
-        <v>2749952.1499100146</v>
+        <v>980928</v>
       </c>
       <c r="E40">
-        <v>13623238.082478862</v>
+        <v>2942817.334415334</v>
       </c>
       <c r="F40">
-        <v>28120953.407683488</v>
+        <v>14578690.462413238</v>
       </c>
       <c r="G40">
-        <v>42618668.740224876</v>
+        <v>30093188.76734814</v>
+      </c>
+      <c r="H40">
+        <v>45607687.08013436</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
-      <c r="C41">
-        <v>26634</v>
+      <c r="B41">
+        <v>8803713</v>
       </c>
       <c r="D41">
-        <v>61674.32041268465</v>
+        <v>28502</v>
       </c>
       <c r="E41">
-        <v>271948.39961068565</v>
+        <v>65999.7881071032</v>
       </c>
       <c r="F41">
-        <v>480305.69399088866</v>
+        <v>291021.2326665472</v>
       </c>
       <c r="G41">
-        <v>529891.356109788</v>
+        <v>513991.46059360553</v>
+      </c>
+      <c r="H41">
+        <v>567054.7642684471</v>
       </c>
     </row>
     <row r="42">
@@ -861,22 +904,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
-        <v>91240</v>
+        <v>11793</v>
       </c>
       <c r="C42">
-        <v>450183</v>
+        <v>97639.02750120258</v>
       </c>
       <c r="D42">
-        <v>69244805.06077418</v>
+        <v>481750</v>
       </c>
       <c r="E42">
-        <v>180666962.896032</v>
+        <v>74101221.23678586</v>
       </c>
       <c r="F42">
-        <v>29792371.47259163</v>
+        <v>193337862.3275363</v>
       </c>
       <c r="G42">
-        <v>6816030.416010834</v>
+        <v>31881830.09138993</v>
+      </c>
+      <c r="H42">
+        <v>7294065.993401086</v>
       </c>
     </row>
     <row r="43">
@@ -904,22 +950,25 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>3880816852</v>
+        <v>4335144028</v>
       </c>
       <c r="C47">
-        <v>3809531295</v>
+        <v>4152994118.1450944</v>
       </c>
       <c r="D47">
-        <v>3521633680.0761876</v>
+        <v>4076659757</v>
       </c>
       <c r="E47">
-        <v>2866773506.7417803</v>
+        <v>3768619988.361685</v>
       </c>
       <c r="F47">
-        <v>2359635294.1123776</v>
+        <v>3067831842.00438</v>
       </c>
       <c r="G47">
-        <v>1721009290.772596</v>
+        <v>2525125990.5156364</v>
+      </c>
+      <c r="H47">
+        <v>1841710581.6699982</v>
       </c>
     </row>
     <row r="48">
@@ -927,22 +976,25 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>6653708866</v>
+        <v>7071404910</v>
       </c>
       <c r="C48">
-        <v>5928258670</v>
+        <v>7120360181.41571</v>
       </c>
       <c r="D48">
-        <v>5813832350.833637</v>
+        <v>6343212715</v>
       </c>
       <c r="E48">
-        <v>4613026296.800502</v>
+        <v>6221579754.38872</v>
       </c>
       <c r="F48">
-        <v>4178615330.9201536</v>
+        <v>4936556350.910509</v>
       </c>
       <c r="G48">
-        <v>4016975138.6191754</v>
+        <v>4471678399.963388</v>
+      </c>
+      <c r="H48">
+        <v>4298701732.039508</v>
       </c>
     </row>
     <row r="49">
@@ -955,22 +1007,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>557118924</v>
+        <v>544657307</v>
       </c>
       <c r="C50">
-        <v>736082611</v>
+        <v>596191910.8053089</v>
       </c>
       <c r="D50">
-        <v>729189996.1697841</v>
+        <v>780822680</v>
       </c>
       <c r="E50">
-        <v>564707339.3297361</v>
+        <v>780331018.0800455</v>
       </c>
       <c r="F50">
-        <v>615014370.9638692</v>
+        <v>604312532.1673284</v>
       </c>
       <c r="G50">
-        <v>1162358295.4194143</v>
+        <v>658147797.8975891</v>
+      </c>
+      <c r="H50">
+        <v>1243879149.1967025</v>
       </c>
     </row>
     <row r="51">
@@ -983,22 +1038,25 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>475048767</v>
+        <v>537297170</v>
       </c>
       <c r="C52">
-        <v>460441037</v>
+        <v>508365844.2078625</v>
       </c>
       <c r="D52">
-        <v>974982293.5529369</v>
+        <v>492727662</v>
       </c>
       <c r="E52">
-        <v>301414182.74024934</v>
+        <v>1043361716.0609466</v>
       </c>
       <c r="F52">
-        <v>318002583.4169137</v>
+        <v>322553569.4632585</v>
       </c>
       <c r="G52">
-        <v>352768763.12300944</v>
+        <v>340305381.2768249</v>
+      </c>
+      <c r="H52">
+        <v>377509852.7414811</v>
       </c>
     </row>
     <row r="53">
@@ -1011,22 +1069,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>41622867</v>
+        <v>37298998</v>
       </c>
       <c r="C54">
-        <v>24779697</v>
+        <v>44542045.76602255</v>
       </c>
       <c r="D54">
-        <v>21871174.48719121</v>
+        <v>26517277</v>
       </c>
       <c r="E54">
-        <v>16337374.027462598</v>
+        <v>23405087.76017605</v>
       </c>
       <c r="F54">
-        <v>15812485.249867843</v>
+        <v>17483179.657659505</v>
       </c>
       <c r="G54">
-        <v>13132720.123318346</v>
+        <v>16921478.322821204</v>
+      </c>
+      <c r="H54">
+        <v>14053770.509494482</v>
       </c>
     </row>
     <row r="55">
@@ -1034,22 +1095,25 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>73894616</v>
+        <v>81581563</v>
       </c>
       <c r="C55">
-        <v>56857511</v>
+        <v>79077142.08477427</v>
       </c>
       <c r="D55">
-        <v>67499677.98951063</v>
+        <v>60844422</v>
       </c>
       <c r="E55">
-        <v>40818661.26722958</v>
+        <v>72233701.39785342</v>
       </c>
       <c r="F55">
-        <v>40331690.26952204</v>
+        <v>43681437.8565684</v>
       </c>
       <c r="G55">
-        <v>93744761.4730074</v>
+        <v>43160313.62774931</v>
+      </c>
+      <c r="H55">
+        <v>100319457.95217717</v>
       </c>
     </row>
     <row r="56">
@@ -1077,22 +1141,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
-        <v>39718425</v>
+        <v>26874636</v>
       </c>
       <c r="C60">
-        <v>48204627</v>
+        <v>42504037.60279978</v>
       </c>
       <c r="D60">
-        <v>23858775.216546584</v>
+        <v>51584788</v>
       </c>
       <c r="E60">
-        <v>71611131.91755529</v>
+        <v>25532086.90830121</v>
       </c>
       <c r="F60">
-        <v>32671724.05673523</v>
+        <v>76633508.0961248</v>
       </c>
       <c r="G60">
-        <v>111507735.14495042</v>
+        <v>34963123.23199554</v>
+      </c>
+      <c r="H60">
+        <v>119328220.28073901</v>
       </c>
     </row>
     <row r="61">
@@ -1100,22 +1167,25 @@
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
       <c r="B61">
-        <v>9675697</v>
+        <v>21196967</v>
       </c>
       <c r="C61">
-        <v>35846818</v>
+        <v>10354292.47562805</v>
       </c>
       <c r="D61">
-        <v>45998656.221149795</v>
+        <v>38360435</v>
       </c>
       <c r="E61">
-        <v>11872171.700876812</v>
+        <v>49224726.652731344</v>
       </c>
       <c r="F61">
-        <v>46267368.48030125</v>
+        <v>12704814.765463721</v>
       </c>
       <c r="G61">
-        <v>10956428.609547343</v>
+        <v>49512284.781416126</v>
+      </c>
+      <c r="H61">
+        <v>11724846.934705785</v>
       </c>
     </row>
     <row r="62">
@@ -1123,22 +1193,25 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>12966345</v>
+        <v>14605288</v>
       </c>
       <c r="C62">
-        <v>9307803</v>
+        <v>13875726.830831658</v>
       </c>
       <c r="D62">
-        <v>14979775.702116286</v>
+        <v>15095483</v>
       </c>
       <c r="E62">
-        <v>6422921.365104571</v>
+        <v>16030367.511407038</v>
       </c>
       <c r="F62">
-        <v>7852294.963334739</v>
+        <v>6873386.626539969</v>
       </c>
       <c r="G62">
-        <v>5294471.751438872</v>
+        <v>8403007.933719806</v>
+      </c>
+      <c r="H62">
+        <v>5665794.311081545</v>
       </c>
     </row>
     <row r="63">
@@ -1146,16 +1219,16 @@
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B63">
-        <v>4460626</v>
+        <v>1316290</v>
       </c>
       <c r="C63">
-        <v>4798529</v>
-      </c>
-      <c r="F63">
-        <v>272328.4066737546</v>
+        <v>4773467.609453959</v>
       </c>
       <c r="G63">
-        <v>190926.61776777284</v>
+        <v>291427.89115056343</v>
+      </c>
+      <c r="H63">
+        <v>204317.0679848659</v>
       </c>
     </row>
     <row r="64">
@@ -1173,22 +1246,25 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>1214506267</v>
+        <v>1264828219</v>
       </c>
       <c r="C66">
-        <v>1376318633</v>
+        <v>1299684467.3826816</v>
       </c>
       <c r="D66">
-        <v>1878380349.3392353</v>
+        <v>1465952747</v>
       </c>
       <c r="E66">
-        <v>1013183782.3482144</v>
+        <v>2010118704.371461</v>
       </c>
       <c r="F66">
-        <v>1076224845.8072178</v>
+        <v>1084242428.6329434</v>
       </c>
       <c r="G66">
-        <v>1749954102.2624538</v>
+        <v>1151704814.9632666</v>
+      </c>
+      <c r="H66">
+        <v>1872685408.9943664</v>
       </c>
     </row>
     <row r="67">
@@ -1201,22 +1277,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
-        <v>687436340</v>
+        <v>641604987</v>
       </c>
       <c r="C68">
-        <v>760063482</v>
+        <v>735649010.3746827</v>
       </c>
       <c r="D68">
-        <v>289885635.44668895</v>
+        <v>738296843</v>
       </c>
       <c r="E68">
-        <v>92511775.6831243</v>
+        <v>310216478.8643451</v>
       </c>
       <c r="F68">
-        <v>53874548.58538497</v>
+        <v>98999997.91878186</v>
       </c>
       <c r="G68">
-        <v>125671788.80973028</v>
+        <v>57652986.967813216</v>
+      </c>
+      <c r="H68">
+        <v>134485655.89345217</v>
       </c>
     </row>
     <row r="69">
@@ -1228,8 +1307,8 @@
       <c r="A70" t="str">
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
-      <c r="F70">
-        <v>3239592.763941768</v>
+      <c r="G70">
+        <v>3466798.410469171</v>
       </c>
     </row>
     <row r="71">
@@ -1246,20 +1325,20 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
-      <c r="B73">
-        <v>942221</v>
-      </c>
       <c r="C73">
-        <v>1728070</v>
+        <v>1008302.7414643861</v>
       </c>
       <c r="D73">
-        <v>2885326.289894928</v>
+        <v>1849244</v>
       </c>
       <c r="E73">
-        <v>7690489.812093219</v>
+        <v>3087685.8063239115</v>
       </c>
       <c r="F73">
-        <v>28581540.81996424</v>
+        <v>8229854.737622622</v>
+      </c>
+      <c r="G73">
+        <v>30586079.0239723</v>
       </c>
     </row>
     <row r="74">
@@ -1297,22 +1376,25 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>18380756</v>
+        <v>18760614</v>
       </c>
       <c r="C80">
-        <v>16317055</v>
+        <v>19669872.21149599</v>
       </c>
       <c r="D80">
-        <v>15322087.874573091</v>
+        <v>17461224</v>
       </c>
       <c r="E80">
-        <v>15977570.132879132</v>
+        <v>16396687.410798823</v>
       </c>
       <c r="F80">
-        <v>11853280.277338576</v>
+        <v>17098141.271444306</v>
       </c>
       <c r="G80">
-        <v>25042950.417828355</v>
+        <v>12684598.410549356</v>
+      </c>
+      <c r="H80">
+        <v>26799313.070556723</v>
       </c>
     </row>
     <row r="81">
@@ -1325,22 +1407,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>148881396</v>
+        <v>194255530</v>
       </c>
       <c r="C82">
-        <v>106390775</v>
+        <v>159323046.01557904</v>
       </c>
       <c r="D82">
-        <v>222270034.03384396</v>
+        <v>235136742</v>
       </c>
       <c r="E82">
-        <v>397780118.3985919</v>
+        <v>237858723.86808115</v>
       </c>
       <c r="F82">
-        <v>353841447.5238327</v>
+        <v>425678035.0696156</v>
       </c>
       <c r="G82">
-        <v>141262409.80118316</v>
+        <v>378657768.80583984</v>
+      </c>
+      <c r="H82">
+        <v>151169709.72669742</v>
       </c>
     </row>
     <row r="83">
@@ -1353,22 +1438,25 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>855640713</v>
+        <v>854621131</v>
       </c>
       <c r="C84">
-        <v>884499382</v>
+        <v>915650231.343222</v>
       </c>
       <c r="D84">
-        <v>530363083.64500093</v>
+        <v>992744053</v>
       </c>
       <c r="E84">
-        <v>513959954.0266885</v>
+        <v>567559575.949549</v>
       </c>
       <c r="F84">
-        <v>451390409.97046226</v>
+        <v>550006028.9974644</v>
       </c>
       <c r="G84">
-        <v>291977149.0287418</v>
+        <v>483048231.61864394</v>
+      </c>
+      <c r="H84">
+        <v>312454678.6907063</v>
       </c>
     </row>
     <row r="85">
@@ -1381,22 +1469,25 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>4581844648</v>
+        <v>4950698676</v>
       </c>
       <c r="C86">
-        <v>3665568930</v>
+        <v>4903187807.894671</v>
       </c>
       <c r="D86">
-        <v>3403637083.4239874</v>
+        <v>3883252071</v>
       </c>
       <c r="E86">
-        <v>3084882650.933102</v>
+        <v>3642347816.665362</v>
       </c>
       <c r="F86">
-        <v>2650281611.281781</v>
+        <v>3301237856.1205597</v>
       </c>
       <c r="G86">
-        <v>1975223812.7729104</v>
+        <v>2836156500.765819</v>
+      </c>
+      <c r="H86">
+        <v>2113754188.6931653</v>
       </c>
     </row>
     <row r="87">
@@ -1407,18 +1498,21 @@
         <v>870000000</v>
       </c>
       <c r="C87">
-        <v>750000000</v>
+        <v>870000000</v>
       </c>
       <c r="D87">
         <v>750000000</v>
       </c>
       <c r="E87">
-        <v>180000000</v>
+        <v>750000000</v>
       </c>
       <c r="F87">
         <v>180000000</v>
       </c>
       <c r="G87">
+        <v>180000000</v>
+      </c>
+      <c r="H87">
         <v>68500000</v>
       </c>
     </row>
@@ -1427,22 +1521,25 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>427298607</v>
+        <v>518266591</v>
       </c>
       <c r="C88">
-        <v>421340351</v>
+        <v>518283366.573266</v>
       </c>
       <c r="D88">
-        <v>421340351.11901206</v>
+        <v>503476006</v>
       </c>
       <c r="E88">
-        <v>764351459.2794611</v>
+        <v>503491152.52276963</v>
       </c>
       <c r="F88">
-        <v>764351459.3096383</v>
+        <v>830582618.4062701</v>
       </c>
       <c r="G88">
-        <v>513631393.38327163</v>
+        <v>830582618.4385637</v>
+      </c>
+      <c r="H88">
+        <v>554458605.0839833</v>
       </c>
     </row>
     <row r="89">
@@ -1475,7 +1572,10 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>786562071</v>
+        <v>841716656</v>
+      </c>
+      <c r="C94">
+        <v>841726826.8497573</v>
       </c>
     </row>
     <row r="95">
@@ -1493,29 +1593,32 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>1190203549</v>
+        <v>1273283549</v>
       </c>
       <c r="C97">
-        <v>1191189590</v>
+        <v>1273677302.2012265</v>
       </c>
       <c r="D97">
-        <v>1192806164.540903</v>
+        <v>1274717095</v>
       </c>
       <c r="E97">
-        <v>1191026394.3288226</v>
+        <v>1276462449.618733</v>
       </c>
       <c r="F97">
-        <v>1005896915.5665565</v>
+        <v>1274557856.9764364</v>
       </c>
       <c r="G97">
-        <v>570413018.7199767</v>
+        <v>1076444504.6293056</v>
+      </c>
+      <c r="H97">
+        <v>610418373.7597959</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
-      <c r="B98">
+      <c r="C98">
         <v>0</v>
       </c>
     </row>
@@ -1524,36 +1627,39 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>24412019</v>
+        <v>26123815</v>
       </c>
       <c r="C99">
-        <v>24412019</v>
+        <v>26124131.899395876</v>
       </c>
       <c r="D99">
-        <v>24412019.375455122</v>
+        <v>26123816</v>
       </c>
       <c r="E99">
-        <v>13353180.20793598</v>
+        <v>26124132.301183175</v>
       </c>
       <c r="F99">
-        <v>13353179.952257352</v>
+        <v>14289692.34492739</v>
       </c>
       <c r="G99">
-        <v>13353179.952257352</v>
+        <v>14289692.071316993</v>
+      </c>
+      <c r="H99">
+        <v>14289692.071316993</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="D100">
-        <v>-62970421.63827728</v>
-      </c>
-      <c r="F100">
-        <v>-62970421.63827728</v>
+      <c r="E100">
+        <v>-67386790.11510387</v>
       </c>
       <c r="G100">
-        <v>117928987.66986416</v>
+        <v>-67386790.11510387</v>
+      </c>
+      <c r="H100">
+        <v>126199821.02462567</v>
       </c>
     </row>
     <row r="101">
@@ -1571,22 +1677,25 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>1341597391</v>
+        <v>1396321130</v>
       </c>
       <c r="C103">
-        <v>761074307</v>
+        <v>1435689002.141502</v>
       </c>
       <c r="D103">
-        <v>761074304.9648018</v>
+        <v>814441662</v>
       </c>
       <c r="E103">
-        <v>749650478.4557027</v>
+        <v>814451501.4567834</v>
       </c>
       <c r="F103">
-        <v>446610574.9216921</v>
+        <v>802226476.131368</v>
       </c>
       <c r="G103">
-        <v>385256393.231954</v>
+        <v>477933167.54830104</v>
+      </c>
+      <c r="H103">
+        <v>412275970.7780455</v>
       </c>
     </row>
     <row r="104">
@@ -1594,22 +1703,25 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>4741432</v>
+        <v>92372910</v>
       </c>
       <c r="C104">
-        <v>580523084</v>
+        <v>5073967.66158573</v>
       </c>
       <c r="D104">
-        <v>316974665.0620928</v>
+        <v>581879467</v>
       </c>
       <c r="E104">
-        <v>249471559.7310202</v>
+        <v>339205370.8809968</v>
       </c>
       <c r="F104">
-        <v>303039903.1699146</v>
+        <v>266968001.768358</v>
       </c>
       <c r="G104">
-        <v>306140839.81558675</v>
+        <v>324293308.19343555</v>
+      </c>
+      <c r="H104">
+        <v>327611725.9753981</v>
       </c>
     </row>
     <row r="105">
@@ -1617,22 +1729,25 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B105">
-        <v>1717238</v>
+        <v>1256884</v>
       </c>
       <c r="C105">
-        <v>1871725</v>
+        <v>1837674.7951349202</v>
       </c>
       <c r="D105">
-        <v>1451834.4254132488</v>
+        <v>1263844</v>
       </c>
       <c r="E105">
-        <v>999909.4924968766</v>
+        <v>1553657.402346743</v>
       </c>
       <c r="F105">
-        <v>718463.860692203</v>
+        <v>1070037.1595420435</v>
       </c>
       <c r="G105">
-        <v>-179925.44493083315</v>
+        <v>768852.6156592086</v>
+      </c>
+      <c r="H105">
+        <v>-192544.33873046612</v>
       </c>
     </row>
     <row r="106">
@@ -1640,22 +1755,25 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>4583561886</v>
+        <v>4951955560</v>
       </c>
       <c r="C106">
-        <v>3667440655</v>
+        <v>4905025482.689807</v>
       </c>
       <c r="D106">
-        <v>3405088917.8494005</v>
+        <v>3884515915</v>
       </c>
       <c r="E106">
-        <v>3085882560.425599</v>
+        <v>3643901474.0677085</v>
       </c>
       <c r="F106">
-        <v>2651000075.1424737</v>
+        <v>3302307893.280102</v>
       </c>
       <c r="G106">
-        <v>1975043887.3279798</v>
+        <v>2836925353.3814783</v>
+      </c>
+      <c r="H106">
+        <v>2113561644.3544352</v>
       </c>
     </row>
     <row r="107">
@@ -1663,22 +1781,25 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>6653708866</v>
+        <v>7071404910</v>
       </c>
       <c r="C107">
-        <v>5928258670</v>
+        <v>7120360181.41571</v>
       </c>
       <c r="D107">
-        <v>5813832350.833637</v>
+        <v>6343212715</v>
       </c>
       <c r="E107">
-        <v>4613026296.800502</v>
+        <v>6221579754.38872</v>
       </c>
       <c r="F107">
-        <v>4178615330.9201536</v>
+        <v>4936556350.910509</v>
       </c>
       <c r="G107">
-        <v>4016975138.6191754</v>
+        <v>4471678399.963388</v>
+      </c>
+      <c r="H107">
+        <v>4298701732.039508</v>
       </c>
     </row>
     <row r="108">
@@ -1686,19 +1807,22 @@
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
       <c r="C108">
+        <v>-685176198.4287411</v>
+      </c>
+      <c r="D108">
         <v>-292328917</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1709,6 +1833,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1716,27 +1842,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1750,28 +1882,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1005476179</v>
+        <v>2249855096</v>
       </c>
       <c r="C3">
-        <v>4231631404.2818604</v>
+        <v>1075981259</v>
       </c>
       <c r="D3">
-        <v>3222430305.021496</v>
+        <v>4528412703.393567</v>
       </c>
       <c r="E3">
-        <v>983576678</v>
+        <v>3448432279.402701</v>
       </c>
       <c r="F3">
-        <v>3997605977.963277</v>
+        <v>2108295572</v>
       </c>
       <c r="G3">
-        <v>3160386149.9823475</v>
+        <v>1052546141</v>
       </c>
       <c r="H3">
-        <v>3815156645.4704413</v>
+        <v>4277974134.3854475</v>
       </c>
       <c r="I3">
-        <v>4405332946.209526</v>
+        <v>3382036718.6820054</v>
+      </c>
+      <c r="J3">
+        <v>4082728897.725605</v>
+      </c>
+      <c r="K3">
+        <v>4714296631.816152</v>
       </c>
     </row>
     <row r="4">
@@ -1783,22 +1921,22 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="C5">
-        <v>4233115770.176569</v>
-      </c>
-      <c r="F5">
-        <v>3877758994.684277</v>
+      <c r="D5">
+        <v>4530001173.827755</v>
+      </c>
+      <c r="H5">
+        <v>4149721801.0194407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="C6">
-        <v>215734684.32135507</v>
-      </c>
-      <c r="F6">
-        <v>330177570.88222384</v>
+      <c r="D6">
+        <v>230865023.84278873</v>
+      </c>
+      <c r="H6">
+        <v>353334249.49199605</v>
       </c>
     </row>
     <row r="7">
@@ -1806,28 +1944,34 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-725072042</v>
+        <v>-1669270037</v>
       </c>
       <c r="C7">
-        <v>-2880611416.2565947</v>
+        <v>-775914879</v>
       </c>
       <c r="D7">
-        <v>-2232094078.758501</v>
+        <v>-3082640259.66852</v>
       </c>
       <c r="E7">
-        <v>-738975248</v>
+        <v>-2388639797.6893106</v>
       </c>
       <c r="F7">
-        <v>-2823962686.52739</v>
+        <v>-1483013852</v>
       </c>
       <c r="G7">
-        <v>-2296697102.0061297</v>
+        <v>-790792993</v>
       </c>
       <c r="H7">
-        <v>-2726076171.2936487</v>
+        <v>-3022018527.0957665</v>
       </c>
       <c r="I7">
-        <v>-3376886187.1430497</v>
+        <v>-2457773690.319035</v>
+      </c>
+      <c r="J7">
+        <v>-2917266837.5637174</v>
+      </c>
+      <c r="K7">
+        <v>-3613720772.6314263</v>
       </c>
     </row>
     <row r="8">
@@ -1835,62 +1979,50 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>280404137</v>
+        <v>580585059</v>
       </c>
       <c r="C8">
-        <v>1351019988.0252657</v>
+        <v>300066380</v>
       </c>
       <c r="D8">
-        <v>990336226.2629944</v>
+        <v>1445772443.725047</v>
       </c>
       <c r="E8">
-        <v>244601430</v>
+        <v>1059792481.7133899</v>
       </c>
       <c r="F8">
-        <v>1173643291.4358869</v>
+        <v>625281720</v>
       </c>
       <c r="G8">
-        <v>863689047.9762177</v>
+        <v>261753148</v>
       </c>
       <c r="H8">
-        <v>1089080474.1767926</v>
+        <v>1255955607.2896807</v>
       </c>
       <c r="I8">
-        <v>1028446759.0664762</v>
+        <v>924263028.3629701</v>
+      </c>
+      <c r="J8">
+        <v>1165462060.1618874</v>
+      </c>
+      <c r="K8">
+        <v>1100575859.1847253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1902,28 +2034,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>280404137</v>
+        <v>580585059</v>
       </c>
       <c r="C13">
-        <v>1351019988.0252657</v>
+        <v>300066380</v>
       </c>
       <c r="D13">
-        <v>990336226.2629944</v>
+        <v>1445772443.725047</v>
       </c>
       <c r="E13">
-        <v>244601430</v>
+        <v>1059792481.7133899</v>
       </c>
       <c r="F13">
-        <v>1173643291.4358869</v>
+        <v>625281720</v>
       </c>
       <c r="G13">
-        <v>863689047.9762177</v>
+        <v>261753148</v>
       </c>
       <c r="H13">
-        <v>1089080474.1767926</v>
+        <v>1255955607.2896807</v>
       </c>
       <c r="I13">
-        <v>1028446759.0664762</v>
+        <v>924263028.3629701</v>
+      </c>
+      <c r="J13">
+        <v>1165462060.1618874</v>
+      </c>
+      <c r="K13">
+        <v>1100575859.1847253</v>
       </c>
     </row>
     <row r="14"/>
@@ -1932,28 +2070,34 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-26178232</v>
+        <v>-52485639</v>
       </c>
       <c r="C15">
-        <v>-85628280.375381</v>
+        <v>-28013878</v>
       </c>
       <c r="D15">
-        <v>-59860444.04962551</v>
+        <v>-91633735.44993983</v>
       </c>
       <c r="E15">
-        <v>-22012182</v>
+        <v>-64058697.31253379</v>
       </c>
       <c r="F15">
-        <v>-66607246.59138215</v>
+        <v>-52974197</v>
       </c>
       <c r="G15">
-        <v>-50645506.84190519</v>
+        <v>-23555700</v>
       </c>
       <c r="H15">
-        <v>-64932415.35791543</v>
+        <v>-71278680.20293011</v>
       </c>
       <c r="I15">
-        <v>-26522580.604047257</v>
+        <v>-54197479.56323021</v>
+      </c>
+      <c r="J15">
+        <v>-69486386.33111589</v>
+      </c>
+      <c r="K15">
+        <v>-28382715.662006054</v>
       </c>
     </row>
     <row r="16">
@@ -1961,28 +2105,34 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-114775229</v>
+        <v>-251556578</v>
       </c>
       <c r="C16">
-        <v>-401067634.7505628</v>
+        <v>-122823392</v>
       </c>
       <c r="D16">
-        <v>-296249424.64292204</v>
+        <v>-429196118.1417412</v>
       </c>
       <c r="E16">
-        <v>-91992362</v>
+        <v>-317026586.1456127</v>
       </c>
       <c r="F16">
-        <v>-332134455.80083495</v>
+        <v>-200241178</v>
       </c>
       <c r="G16">
-        <v>-277956227.7423275</v>
+        <v>-98442966</v>
       </c>
       <c r="H16">
-        <v>-305956895.15302235</v>
+        <v>-355428378.60625464</v>
       </c>
       <c r="I16">
-        <v>-379769862.59172255</v>
+        <v>-297450413.904687</v>
+      </c>
+      <c r="J16">
+        <v>-327414880.53516555</v>
+      </c>
+      <c r="K16">
+        <v>-406404647.7172416</v>
       </c>
     </row>
     <row r="17">
@@ -1995,28 +2145,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>29160674</v>
+        <v>43009601</v>
       </c>
       <c r="C18">
-        <v>60615720.3780561</v>
+        <v>31205452</v>
       </c>
       <c r="D18">
-        <v>87684064.92356305</v>
+        <v>64866944.202084884</v>
       </c>
       <c r="E18">
-        <v>35959914</v>
+        <v>93833700.42184354</v>
       </c>
       <c r="F18">
-        <v>59248620.95823124</v>
+        <v>33836256</v>
       </c>
       <c r="G18">
-        <v>43986929.85086214</v>
+        <v>38481462</v>
       </c>
       <c r="H18">
-        <v>51690877.7880388</v>
+        <v>63403964.61145405</v>
       </c>
       <c r="I18">
-        <v>48084849.50740374</v>
+        <v>47071909.835618116</v>
+      </c>
+      <c r="J18">
+        <v>55316166.57066661</v>
+      </c>
+      <c r="K18">
+        <v>51457233.04958988</v>
       </c>
     </row>
     <row r="19">
@@ -2024,28 +2180,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-38551868</v>
+        <v>-43409741</v>
       </c>
       <c r="C19">
-        <v>-36145145.74686599</v>
+        <v>-41255167</v>
       </c>
       <c r="D19">
-        <v>-61635855.351583794</v>
+        <v>-38680149.93000026</v>
       </c>
       <c r="E19">
-        <v>-12304428</v>
+        <v>-65958625.33684167</v>
       </c>
       <c r="F19">
-        <v>-90960583.35866153</v>
+        <v>-26716943</v>
       </c>
       <c r="G19">
-        <v>-79766294.6082822</v>
+        <v>-13167228</v>
       </c>
       <c r="H19">
-        <v>-50865703.69917618</v>
+        <v>-97340014.24903312</v>
       </c>
       <c r="I19">
-        <v>-35907304.49313083</v>
+        <v>-85360625.08688176</v>
+      </c>
+      <c r="J19">
+        <v>-54433119.71012587</v>
+      </c>
+      <c r="K19">
+        <v>-38425627.91427944</v>
       </c>
     </row>
     <row r="20">
@@ -2058,28 +2220,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>130059482</v>
+        <v>276142702</v>
       </c>
       <c r="C21">
-        <v>888794647.530512</v>
+        <v>139179395</v>
       </c>
       <c r="D21">
-        <v>660274567.142426</v>
+        <v>951129384.4054506</v>
       </c>
       <c r="E21">
-        <v>154252372</v>
+        <v>706582273.3402451</v>
       </c>
       <c r="F21">
-        <v>743189626.6432395</v>
+        <v>379185658</v>
       </c>
       <c r="G21">
-        <v>499307948.634565</v>
+        <v>165068716</v>
       </c>
       <c r="H21">
-        <v>719016337.7547176</v>
+        <v>795312498.8429168</v>
       </c>
       <c r="I21">
-        <v>634331860.8849792</v>
+        <v>534326419.6437893</v>
+      </c>
+      <c r="J21">
+        <v>769443840.1561468</v>
+      </c>
+      <c r="K21">
+        <v>678820100.940788</v>
       </c>
     </row>
     <row r="22"/>
@@ -2098,25 +2266,31 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>22650850</v>
+        <v>44734895</v>
       </c>
       <c r="C25">
-        <v>3530721.7278499203</v>
+        <v>24239152</v>
       </c>
       <c r="D25">
-        <v>2775157.237863876</v>
+        <v>3778345.4174115723</v>
       </c>
       <c r="E25">
-        <v>1661145</v>
+        <v>2969790.156378259</v>
       </c>
       <c r="F25">
-        <v>11481480.060002219</v>
+        <v>2767989</v>
       </c>
       <c r="G25">
-        <v>10988514.59808982</v>
+        <v>1777626</v>
       </c>
       <c r="H25">
-        <v>50925929.95289289</v>
+        <v>12286722.351304973</v>
+      </c>
+      <c r="I25">
+        <v>11759183.242440354</v>
+      </c>
+      <c r="J25">
+        <v>54497569.872806065</v>
       </c>
     </row>
     <row r="26">
@@ -2159,28 +2333,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>152710332</v>
+        <v>320877597</v>
       </c>
       <c r="C33">
-        <v>892325369.2583618</v>
+        <v>163418547</v>
       </c>
       <c r="D33">
-        <v>663049724.38029</v>
+        <v>954907729.822862</v>
       </c>
       <c r="E33">
-        <v>155913517</v>
+        <v>709552063.4966235</v>
       </c>
       <c r="F33">
-        <v>754671106.7032417</v>
+        <v>381953647</v>
       </c>
       <c r="G33">
-        <v>510296463.23265487</v>
+        <v>166846342</v>
       </c>
       <c r="H33">
-        <v>769942267.7076104</v>
+        <v>807599221.1942219</v>
       </c>
       <c r="I33">
-        <v>634331860.8849792</v>
+        <v>546085602.8862298</v>
+      </c>
+      <c r="J33">
+        <v>823941410.0289527</v>
+      </c>
+      <c r="K33">
+        <v>678820100.940788</v>
       </c>
     </row>
     <row r="34"/>
@@ -2189,28 +2369,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>41705422</v>
+        <v>79899922</v>
       </c>
       <c r="C35">
-        <v>105864860.15434265</v>
+        <v>44629851</v>
       </c>
       <c r="D35">
-        <v>96021626.44379637</v>
+        <v>113289587.81259127</v>
       </c>
       <c r="E35">
-        <v>10715275</v>
+        <v>102756008.60429673</v>
       </c>
       <c r="F35">
-        <v>87146164.02506068</v>
+        <v>37567613</v>
       </c>
       <c r="G35">
-        <v>57930326.17086499</v>
+        <v>11466642</v>
       </c>
       <c r="H35">
-        <v>93820612.14818752</v>
+        <v>93258074.37381862</v>
       </c>
       <c r="I35">
-        <v>105550391.05443066</v>
+        <v>61993212.51809209</v>
+      </c>
+      <c r="J35">
+        <v>100400628.33972536</v>
+      </c>
+      <c r="K35">
+        <v>112953063.73220344</v>
       </c>
     </row>
     <row r="36">
@@ -2218,28 +2404,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-74807625</v>
+        <v>-212396445</v>
       </c>
       <c r="C36">
-        <v>-359595510.96267647</v>
+        <v>-80053217</v>
       </c>
       <c r="D36">
-        <v>-309192406.6885443</v>
+        <v>-384815387.8144866</v>
       </c>
       <c r="E36">
-        <v>-63177232</v>
+        <v>-330877311.4842809</v>
       </c>
       <c r="F36">
-        <v>-302043944.3709699</v>
+        <v>-141686992</v>
       </c>
       <c r="G36">
-        <v>-194331711.5787326</v>
+        <v>-67607288</v>
       </c>
       <c r="H36">
-        <v>-242100640.2450092</v>
+        <v>-323227498.8054453</v>
       </c>
       <c r="I36">
-        <v>-342612778.93039954</v>
+        <v>-207960974.69521746</v>
+      </c>
+      <c r="J36">
+        <v>-259080130.10676464</v>
+      </c>
+      <c r="K36">
+        <v>-366641588.6042166</v>
       </c>
     </row>
     <row r="37">
@@ -2247,28 +2439,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-57558596</v>
+        <v>-96441420</v>
       </c>
       <c r="C37">
-        <v>-155907557.190266</v>
+        <v>-61594667</v>
       </c>
       <c r="D37">
-        <v>-224371398.14414266</v>
+        <v>-166841980.09804577</v>
       </c>
       <c r="E37">
-        <v>-12988499</v>
+        <v>-240107465.079781</v>
       </c>
       <c r="F37">
-        <v>-217481439.2493974</v>
+        <v>-101163964</v>
       </c>
       <c r="G37">
-        <v>-210344862.58486822</v>
+        <v>-13899267</v>
       </c>
       <c r="H37">
-        <v>-139529083.1528917</v>
+        <v>-232734285.70663118</v>
       </c>
       <c r="I37">
-        <v>-49434952.94112057</v>
+        <v>-225097192.26940623</v>
+      </c>
+      <c r="J37">
+        <v>-149314817.92177525</v>
+      </c>
+      <c r="K37">
+        <v>-52902024.65737315</v>
       </c>
     </row>
     <row r="38">
@@ -2276,28 +2474,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>62049533</v>
+        <v>91939654</v>
       </c>
       <c r="C38">
-        <v>482687161.25976205</v>
+        <v>66400514</v>
       </c>
       <c r="D38">
-        <v>225507545.9913994</v>
+        <v>516539949.72292095</v>
       </c>
       <c r="E38">
-        <v>90463061</v>
+        <v>241323295.5368583</v>
       </c>
       <c r="F38">
-        <v>322291887.10793513</v>
+        <v>176670304</v>
       </c>
       <c r="G38">
-        <v>163550215.23991898</v>
+        <v>96806429</v>
       </c>
       <c r="H38">
-        <v>482133156.45789707</v>
+        <v>344895511.055964</v>
       </c>
       <c r="I38">
-        <v>347834520.06788987</v>
+        <v>175020648.43969804</v>
+      </c>
+      <c r="J38">
+        <v>515947090.34013826</v>
+      </c>
+      <c r="K38">
+        <v>372229551.4114018</v>
       </c>
     </row>
     <row r="39"/>
@@ -2306,28 +2510,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-57462588</v>
+        <v>426296</v>
       </c>
       <c r="C40">
-        <v>61938276.91447321</v>
+        <v>-61491927</v>
       </c>
       <c r="D40">
-        <v>91919043.34645197</v>
+        <v>66282256.93806829</v>
       </c>
       <c r="E40">
-        <v>-46112975</v>
+        <v>98365694.88369636</v>
       </c>
       <c r="F40">
-        <v>-72538881.2346615</v>
+        <v>-15581092</v>
       </c>
       <c r="G40">
-        <v>-40941585.875149235</v>
+        <v>-49346467</v>
       </c>
       <c r="H40">
-        <v>-178194863.98235932</v>
+        <v>-77626324.1974746</v>
       </c>
       <c r="I40">
-        <v>-41428449.78397016</v>
+        <v>-43812983.66074686</v>
+      </c>
+      <c r="J40">
+        <v>-190692385.19231296</v>
+      </c>
+      <c r="K40">
+        <v>-44333993.2901058</v>
       </c>
     </row>
     <row r="41">
@@ -2335,28 +2545,34 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-14633699</v>
+        <v>-40003699</v>
       </c>
       <c r="C41">
-        <v>-116800794.98290488</v>
+        <v>-15659830</v>
       </c>
       <c r="D41">
-        <v>-84184297.86707136</v>
+        <v>-124992503.65517507</v>
       </c>
       <c r="E41">
-        <v>-14681771</v>
+        <v>-90088480.65116626</v>
       </c>
       <c r="F41">
-        <v>-72661262.47119558</v>
+        <v>-46247169</v>
       </c>
       <c r="G41">
-        <v>-60694111.31952174</v>
+        <v>-15711273</v>
       </c>
       <c r="H41">
-        <v>-133778677.09484382</v>
+        <v>-77757288.52145073</v>
       </c>
       <c r="I41">
-        <v>-52503256.98465203</v>
+        <v>-64950833.014991604</v>
+      </c>
+      <c r="J41">
+        <v>-143161112.80072287</v>
+      </c>
+      <c r="K41">
+        <v>-56185521.18179686</v>
       </c>
     </row>
     <row r="42">
@@ -2364,28 +2580,34 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-42828889</v>
+        <v>40429995</v>
       </c>
       <c r="C42">
-        <v>178739071.89737812</v>
+        <v>-45832097</v>
       </c>
       <c r="D42">
-        <v>176103341.2135233</v>
+        <v>191274760.5932434</v>
       </c>
       <c r="E42">
-        <v>-31431204</v>
+        <v>188454175.53486258</v>
       </c>
       <c r="F42">
-        <v>122381.2365340778</v>
+        <v>30666077</v>
       </c>
       <c r="G42">
-        <v>19752525.44437251</v>
+        <v>-33635194</v>
       </c>
       <c r="H42">
-        <v>44416186.887515515</v>
+        <v>130964.3239761289</v>
       </c>
       <c r="I42">
-        <v>11074807.200681867</v>
+        <v>21137849.35424475</v>
+      </c>
+      <c r="J42">
+        <v>47531272.391590096</v>
+      </c>
+      <c r="K42">
+        <v>11851527.891691068</v>
       </c>
     </row>
     <row r="43">
@@ -2393,28 +2615,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>4586945</v>
+        <v>92365950</v>
       </c>
       <c r="C43">
-        <v>544625438.1742352</v>
+        <v>4908587</v>
       </c>
       <c r="D43">
-        <v>317426589.3378514</v>
+        <v>582822206.6609892</v>
       </c>
       <c r="E43">
-        <v>44350086</v>
+        <v>339688990.4205547</v>
       </c>
       <c r="F43">
-        <v>249753005.87327364</v>
+        <v>161089212</v>
       </c>
       <c r="G43">
-        <v>122608629.36476976</v>
+        <v>47459962</v>
       </c>
       <c r="H43">
-        <v>303938292.47553766</v>
+        <v>267269186.85848942</v>
       </c>
       <c r="I43">
-        <v>306406070.28391963</v>
+        <v>131207664.77895121</v>
+      </c>
+      <c r="J43">
+        <v>325254705.14782524</v>
+      </c>
+      <c r="K43">
+        <v>327895558.1212959</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2656,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>4586945</v>
+        <v>92365950</v>
       </c>
       <c r="C46">
-        <v>544625438.1742352</v>
+        <v>4908587</v>
       </c>
       <c r="D46">
-        <v>317426589.3378514</v>
+        <v>582822206.6609892</v>
       </c>
       <c r="E46">
-        <v>44350086</v>
+        <v>339688990.4205547</v>
       </c>
       <c r="F46">
-        <v>249753005.87327364</v>
+        <v>161089212</v>
       </c>
       <c r="G46">
-        <v>122608629.36476976</v>
+        <v>47459962</v>
       </c>
       <c r="H46">
-        <v>303938292.47553766</v>
+        <v>267269186.85848942</v>
       </c>
       <c r="I46">
-        <v>306406070.28391963</v>
+        <v>131207664.77895121</v>
+      </c>
+      <c r="J46">
+        <v>325254705.14782524</v>
+      </c>
+      <c r="K46">
+        <v>327895558.1212959</v>
       </c>
     </row>
     <row r="47">
@@ -2457,28 +2691,34 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>-154487</v>
+        <v>-6960</v>
       </c>
       <c r="C47">
-        <v>874385.4506114341</v>
+        <v>-165319</v>
       </c>
       <c r="D47">
-        <v>451924.27575863764</v>
+        <v>935709.6126578389</v>
       </c>
       <c r="E47">
-        <v>161085</v>
+        <v>483619.5395578549</v>
       </c>
       <c r="F47">
-        <v>281446.1422534129</v>
+        <v>287213</v>
       </c>
       <c r="G47">
-        <v>181573.3241605835</v>
+        <v>172380</v>
       </c>
       <c r="H47">
-        <v>898389.3056230361</v>
+        <v>301185.09013139363</v>
       </c>
       <c r="I47">
-        <v>265231.61668082274</v>
+        <v>194307.7903463391</v>
+      </c>
+      <c r="J47">
+        <v>961396.9543896746</v>
+      </c>
+      <c r="K47">
+        <v>283833.37478394643</v>
       </c>
     </row>
     <row r="48">
@@ -2486,28 +2726,34 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>4741432</v>
+        <v>92372910</v>
       </c>
       <c r="C48">
-        <v>543751052.7236238</v>
+        <v>5073906</v>
       </c>
       <c r="D48">
-        <v>316974665.0620928</v>
+        <v>581886497.0483314</v>
       </c>
       <c r="E48">
-        <v>44189001</v>
+        <v>339205370.8809968</v>
       </c>
       <c r="F48">
-        <v>249471559.7310202</v>
+        <v>160801999</v>
       </c>
       <c r="G48">
-        <v>122427056.04060917</v>
+        <v>47287582</v>
       </c>
       <c r="H48">
-        <v>303039903.1699146</v>
+        <v>266968001.768358</v>
       </c>
       <c r="I48">
-        <v>306140838.66723883</v>
+        <v>131013356.98860486</v>
+      </c>
+      <c r="J48">
+        <v>324293308.19343555</v>
+      </c>
+      <c r="K48">
+        <v>327611724.746512</v>
       </c>
     </row>
     <row r="49"/>
@@ -2516,40 +2762,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>28565000</v>
+        <v>77801908</v>
       </c>
       <c r="C50">
-        <v>145881911.28227282</v>
+        <v>30568378.129897542</v>
       </c>
       <c r="D50">
-        <v>104456041.92221476</v>
+        <v>156113195.3925672</v>
       </c>
       <c r="E50">
-        <v>35646699</v>
+        <v>111781963.50186208</v>
       </c>
       <c r="F50">
-        <v>103724450.1488672</v>
+        <v>62764306</v>
       </c>
       <c r="G50">
-        <v>57181966.22106663</v>
+        <v>38146745.111662544</v>
       </c>
       <c r="H50">
-        <v>107375616.53973901</v>
+        <v>110999062.26032837</v>
       </c>
       <c r="I50">
-        <v>64584697.911915466</v>
+        <v>61192367.08057389</v>
+      </c>
+      <c r="J50">
+        <v>114906299.60852872</v>
+      </c>
+      <c r="K50">
+        <v>69114282.06464681</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2560,6 +2812,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2567,27 +2821,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2601,16 +2861,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1005476179</v>
+        <v>1173873837</v>
       </c>
       <c r="C3">
-        <v>1009201099.2603645</v>
+        <v>1075981259</v>
+      </c>
+      <c r="D3">
+        <v>1079980423.9908662</v>
       </c>
       <c r="E3">
-        <v>983576678</v>
+        <v>1340136707.402701</v>
       </c>
       <c r="F3">
-        <v>837219827.9809294</v>
+        <v>1055749431</v>
+      </c>
+      <c r="G3">
+        <v>1052546141</v>
+      </c>
+      <c r="H3">
+        <v>895937415.7034421</v>
       </c>
     </row>
     <row r="4">
@@ -2633,16 +2902,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-725072042</v>
+        <v>-893355158</v>
       </c>
       <c r="C7">
-        <v>-648517337.4980936</v>
+        <v>-775914879</v>
+      </c>
+      <c r="D7">
+        <v>-694000461.9792094</v>
       </c>
       <c r="E7">
-        <v>-738975248</v>
+        <v>-905625945.6893106</v>
       </c>
       <c r="F7">
-        <v>-527265584.52126026</v>
+        <v>-692220859</v>
+      </c>
+      <c r="G7">
+        <v>-790792993</v>
+      </c>
+      <c r="H7">
+        <v>-564244836.7767315</v>
       </c>
     </row>
     <row r="8">
@@ -2650,50 +2928,41 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>280404137</v>
+        <v>280518679</v>
       </c>
       <c r="C8">
-        <v>360683761.7622713</v>
+        <v>300066380</v>
+      </c>
+      <c r="D8">
+        <v>385979962.01165724</v>
       </c>
       <c r="E8">
-        <v>244601430</v>
+        <v>434510761.7133899</v>
       </c>
       <c r="F8">
-        <v>309954243.4596691</v>
+        <v>363528572</v>
+      </c>
+      <c r="G8">
+        <v>261753148</v>
+      </c>
+      <c r="H8">
+        <v>331692578.9267106</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -2705,16 +2974,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>280404137</v>
+        <v>280518679</v>
       </c>
       <c r="C13">
-        <v>360683761.7622713</v>
+        <v>300066380</v>
+      </c>
+      <c r="D13">
+        <v>385979962.01165724</v>
       </c>
       <c r="E13">
-        <v>244601430</v>
+        <v>434510761.7133899</v>
       </c>
       <c r="F13">
-        <v>309954243.4596691</v>
+        <v>363528572</v>
+      </c>
+      <c r="G13">
+        <v>261753148</v>
+      </c>
+      <c r="H13">
+        <v>331692578.9267106</v>
       </c>
     </row>
     <row r="14"/>
@@ -2723,16 +3001,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-26178232</v>
+        <v>-24471761</v>
       </c>
       <c r="C15">
-        <v>-25767836.325755484</v>
+        <v>-28013878</v>
+      </c>
+      <c r="D15">
+        <v>-27575038.137406044</v>
       </c>
       <c r="E15">
-        <v>-22012182</v>
+        <v>-11084500.312533788</v>
       </c>
       <c r="F15">
-        <v>-15961739.749476962</v>
+        <v>-29418497</v>
+      </c>
+      <c r="G15">
+        <v>-23555700</v>
+      </c>
+      <c r="H15">
+        <v>-17081200.6396999</v>
       </c>
     </row>
     <row r="16">
@@ -2740,16 +3027,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-114775229</v>
+        <v>-128733186</v>
       </c>
       <c r="C16">
-        <v>-104818210.10764074</v>
+        <v>-122823392</v>
+      </c>
+      <c r="D16">
+        <v>-112169531.9961285</v>
       </c>
       <c r="E16">
-        <v>-91992362</v>
+        <v>-116785408.14561272</v>
       </c>
       <c r="F16">
-        <v>-54178228.05850744</v>
+        <v>-101798212</v>
+      </c>
+      <c r="G16">
+        <v>-98442966</v>
+      </c>
+      <c r="H16">
+        <v>-57977964.70156765</v>
       </c>
     </row>
     <row r="17">
@@ -2762,16 +3058,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>29160674</v>
+        <v>11804149</v>
       </c>
       <c r="C18">
-        <v>-27068344.545506947</v>
+        <v>31205452</v>
+      </c>
+      <c r="D18">
+        <v>-28966756.21975866</v>
       </c>
       <c r="E18">
-        <v>35959914</v>
+        <v>59997444.42184354</v>
       </c>
       <c r="F18">
-        <v>15261691.107369103</v>
+        <v>-4645206</v>
+      </c>
+      <c r="G18">
+        <v>38481462</v>
+      </c>
+      <c r="H18">
+        <v>16332054.775835931</v>
       </c>
     </row>
     <row r="19">
@@ -2779,16 +3084,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-38551868</v>
+        <v>-2154574</v>
       </c>
       <c r="C19">
-        <v>25490709.604717806</v>
+        <v>-41255167</v>
+      </c>
+      <c r="D19">
+        <v>27278475.406841412</v>
       </c>
       <c r="E19">
-        <v>-12304428</v>
+        <v>-39241682.33684167</v>
       </c>
       <c r="F19">
-        <v>-11194288.750379339</v>
+        <v>-13549715</v>
+      </c>
+      <c r="G19">
+        <v>-13167228</v>
+      </c>
+      <c r="H19">
+        <v>-11979389.162151366</v>
       </c>
     </row>
     <row r="20">
@@ -2801,16 +3115,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>130059482</v>
+        <v>136963307</v>
       </c>
       <c r="C21">
-        <v>228520080.38808596</v>
+        <v>139179395</v>
+      </c>
+      <c r="D21">
+        <v>244547111.06520545</v>
       </c>
       <c r="E21">
-        <v>154252372</v>
+        <v>327396615.3402451</v>
       </c>
       <c r="F21">
-        <v>243881678.0086745</v>
+        <v>214116942</v>
+      </c>
+      <c r="G21">
+        <v>165068716</v>
+      </c>
+      <c r="H21">
+        <v>260986079.19912755</v>
       </c>
     </row>
     <row r="22"/>
@@ -2829,16 +3152,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>22650850</v>
+        <v>20495743</v>
       </c>
       <c r="C25">
-        <v>755564.4899860444</v>
+        <v>24239152</v>
+      </c>
+      <c r="D25">
+        <v>808555.2610333133</v>
       </c>
       <c r="E25">
-        <v>1661145</v>
+        <v>201801.15637825895</v>
       </c>
       <c r="F25">
-        <v>492965.46191239916</v>
+        <v>990363</v>
+      </c>
+      <c r="G25">
+        <v>1777626</v>
+      </c>
+      <c r="H25">
+        <v>527539.1088646185</v>
       </c>
     </row>
     <row r="26">
@@ -2881,16 +3213,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>152710332</v>
+        <v>157459050</v>
       </c>
       <c r="C33">
-        <v>229275644.87807178</v>
+        <v>163418547</v>
+      </c>
+      <c r="D33">
+        <v>245355666.3262385</v>
       </c>
       <c r="E33">
-        <v>155913517</v>
+        <v>327598416.4966235</v>
       </c>
       <c r="F33">
-        <v>244374643.47058684</v>
+        <v>215107305</v>
+      </c>
+      <c r="G33">
+        <v>166846342</v>
+      </c>
+      <c r="H33">
+        <v>261513618.3079921</v>
       </c>
     </row>
     <row r="34"/>
@@ -2899,16 +3240,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>41705422</v>
+        <v>35270071</v>
       </c>
       <c r="C35">
-        <v>9843233.710546285</v>
+        <v>44629851</v>
+      </c>
+      <c r="D35">
+        <v>10533579.20829454</v>
       </c>
       <c r="E35">
-        <v>10715275</v>
+        <v>65188395.60429673</v>
       </c>
       <c r="F35">
-        <v>29215837.85419569</v>
+        <v>26100971</v>
+      </c>
+      <c r="G35">
+        <v>11466642</v>
+      </c>
+      <c r="H35">
+        <v>31264861.855726533</v>
       </c>
     </row>
     <row r="36">
@@ -2916,16 +3266,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-74807625</v>
+        <v>-132343228</v>
       </c>
       <c r="C36">
-        <v>-50403104.27413219</v>
+        <v>-80053217</v>
+      </c>
+      <c r="D36">
+        <v>-53938076.33020574</v>
       </c>
       <c r="E36">
-        <v>-63177232</v>
+        <v>-189190319.48428088</v>
       </c>
       <c r="F36">
-        <v>-107712232.79223728</v>
+        <v>-74079704</v>
+      </c>
+      <c r="G36">
+        <v>-67607288</v>
+      </c>
+      <c r="H36">
+        <v>-115266524.11022785</v>
       </c>
     </row>
     <row r="37">
@@ -2933,16 +3292,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-57558596</v>
+        <v>-34846753</v>
       </c>
       <c r="C37">
-        <v>68463840.95387664</v>
+        <v>-61594667</v>
+      </c>
+      <c r="D37">
+        <v>73265484.98173523</v>
       </c>
       <c r="E37">
-        <v>-12988499</v>
+        <v>-138943501.079781</v>
       </c>
       <c r="F37">
-        <v>-7136576.664529175</v>
+        <v>-87264697</v>
+      </c>
+      <c r="G37">
+        <v>-13899267</v>
+      </c>
+      <c r="H37">
+        <v>-7637093.437224954</v>
       </c>
     </row>
     <row r="38">
@@ -2950,16 +3318,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>62049533</v>
+        <v>25539140</v>
       </c>
       <c r="C38">
-        <v>257179615.26836264</v>
+        <v>66400514</v>
+      </c>
+      <c r="D38">
+        <v>275216654.1860627</v>
       </c>
       <c r="E38">
-        <v>90463061</v>
+        <v>64652991.53685829</v>
       </c>
       <c r="F38">
-        <v>158741671.86801615</v>
+        <v>79863875</v>
+      </c>
+      <c r="G38">
+        <v>96806429</v>
+      </c>
+      <c r="H38">
+        <v>169874862.61626595</v>
       </c>
     </row>
     <row r="39"/>
@@ -2968,16 +3345,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-57462588</v>
+        <v>61918223</v>
       </c>
       <c r="C40">
-        <v>-29980766.431978755</v>
+        <v>-61491927</v>
+      </c>
+      <c r="D40">
+        <v>-32083437.94562807</v>
       </c>
       <c r="E40">
-        <v>-46112975</v>
+        <v>113946786.88369636</v>
       </c>
       <c r="F40">
-        <v>-31597295.35951227</v>
+        <v>33765375</v>
+      </c>
+      <c r="G40">
+        <v>-49346467</v>
+      </c>
+      <c r="H40">
+        <v>-33813340.53672774</v>
       </c>
     </row>
     <row r="41">
@@ -2985,16 +3371,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-14633699</v>
+        <v>-24343869</v>
       </c>
       <c r="C41">
-        <v>-32616497.11583352</v>
+        <v>-15659830</v>
+      </c>
+      <c r="D41">
+        <v>-34904023.004008815</v>
       </c>
       <c r="E41">
-        <v>-14681771</v>
+        <v>-43841311.65116626</v>
       </c>
       <c r="F41">
-        <v>-11967151.151673838</v>
+        <v>-30535896</v>
+      </c>
+      <c r="G41">
+        <v>-15711273</v>
+      </c>
+      <c r="H41">
+        <v>-12806455.506459124</v>
       </c>
     </row>
     <row r="42">
@@ -3002,16 +3397,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-42828889</v>
+        <v>86262092</v>
       </c>
       <c r="C42">
-        <v>2635730.6838548183</v>
+        <v>-45832097</v>
+      </c>
+      <c r="D42">
+        <v>2820585.0583808124</v>
       </c>
       <c r="E42">
-        <v>-31431204</v>
+        <v>157788098.53486258</v>
       </c>
       <c r="F42">
-        <v>-19630144.20783843</v>
+        <v>64301271</v>
+      </c>
+      <c r="G42">
+        <v>-33635194</v>
+      </c>
+      <c r="H42">
+        <v>-21006885.03026862</v>
       </c>
     </row>
     <row r="43">
@@ -3019,16 +3423,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>4586945</v>
+        <v>87457363</v>
       </c>
       <c r="C43">
-        <v>227198848.83638382</v>
+        <v>4908587</v>
+      </c>
+      <c r="D43">
+        <v>243133216.24043447</v>
       </c>
       <c r="E43">
-        <v>44350086</v>
+        <v>178599778.4205547</v>
       </c>
       <c r="F43">
-        <v>127144376.50850388</v>
+        <v>113629250</v>
+      </c>
+      <c r="G43">
+        <v>47459962</v>
+      </c>
+      <c r="H43">
+        <v>136061522.07953823</v>
       </c>
     </row>
     <row r="44">
@@ -3042,16 +3455,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>4586945</v>
+        <v>87457363</v>
       </c>
       <c r="C46">
-        <v>227198848.83638382</v>
+        <v>4908587</v>
+      </c>
+      <c r="D46">
+        <v>243133216.24043447</v>
       </c>
       <c r="E46">
-        <v>44350086</v>
+        <v>178599778.4205547</v>
       </c>
       <c r="F46">
-        <v>127144376.50850388</v>
+        <v>113629250</v>
+      </c>
+      <c r="G46">
+        <v>47459962</v>
+      </c>
+      <c r="H46">
+        <v>136061522.07953823</v>
       </c>
     </row>
     <row r="47">
@@ -3059,16 +3481,25 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>-154487</v>
+        <v>158359</v>
       </c>
       <c r="C47">
-        <v>422461.1748527964</v>
+        <v>-165319</v>
+      </c>
+      <c r="D47">
+        <v>452090.073099984</v>
       </c>
       <c r="E47">
-        <v>161085</v>
+        <v>196406.53955785488</v>
       </c>
       <c r="F47">
-        <v>99872.81809282943</v>
+        <v>114833</v>
+      </c>
+      <c r="G47">
+        <v>172380</v>
+      </c>
+      <c r="H47">
+        <v>106877.29978505452</v>
       </c>
     </row>
     <row r="48">
@@ -3076,16 +3507,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>4741432</v>
+        <v>87299004</v>
       </c>
       <c r="C48">
-        <v>226776387.66153097</v>
+        <v>5073906</v>
+      </c>
+      <c r="D48">
+        <v>242681126.16733456</v>
       </c>
       <c r="E48">
-        <v>44189001</v>
+        <v>178403371.88099682</v>
       </c>
       <c r="F48">
-        <v>127044503.69041105</v>
+        <v>113514417</v>
+      </c>
+      <c r="G48">
+        <v>47287582</v>
+      </c>
+      <c r="H48">
+        <v>135954644.77975315</v>
       </c>
     </row>
     <row r="49"/>
@@ -3094,28 +3534,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>28565000</v>
+        <v>47233529.87010246</v>
       </c>
       <c r="C50">
-        <v>41425869.360058054</v>
+        <v>30568378.129897542</v>
+      </c>
+      <c r="D50">
+        <v>44331231.89070511</v>
       </c>
       <c r="E50">
-        <v>35646699</v>
+        <v>49017657.50186208</v>
       </c>
       <c r="F50">
-        <v>46542483.92780057</v>
+        <v>24617560.888337456</v>
+      </c>
+      <c r="G50">
+        <v>38146745.111662544</v>
+      </c>
+      <c r="H50">
+        <v>49806695.17975448</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3126,6 +3575,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3133,27 +3584,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3167,22 +3624,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>4253530905.2818604</v>
+        <v>4669972227.393567</v>
       </c>
       <c r="C3">
-        <v>4231631404.2818604</v>
+        <v>4551847821.393567</v>
       </c>
       <c r="D3">
-        <v>4059650133.002425</v>
-      </c>
-      <c r="F3">
-        <v>3997605977.963277</v>
+        <v>4528412703.393567</v>
+      </c>
+      <c r="E3">
+        <v>4344369695.106143</v>
       </c>
       <c r="H3">
-        <v>3815156645.4704413</v>
-      </c>
-      <c r="I3">
-        <v>4405332946.209526</v>
+        <v>4277974134.3854475</v>
+      </c>
+      <c r="J3">
+        <v>4082728897.725605</v>
+      </c>
+      <c r="K3">
+        <v>4714296631.816152</v>
       </c>
     </row>
     <row r="4">
@@ -3194,22 +3654,22 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="C5">
-        <v>4233115770.176569</v>
-      </c>
-      <c r="F5">
-        <v>3877758994.684277</v>
+      <c r="D5">
+        <v>4530001173.827755</v>
+      </c>
+      <c r="H5">
+        <v>4149721801.0194407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="C6">
-        <v>215734684.32135507</v>
-      </c>
-      <c r="F6">
-        <v>330177570.88222384</v>
+      <c r="D6">
+        <v>230865023.84278873</v>
+      </c>
+      <c r="H6">
+        <v>353334249.49199605</v>
       </c>
     </row>
     <row r="7">
@@ -3217,22 +3677,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-2866708210.2565947</v>
+        <v>-3268896444.66852</v>
       </c>
       <c r="C7">
-        <v>-2880611416.2565947</v>
+        <v>-3067762145.66852</v>
       </c>
       <c r="D7">
-        <v>-2759359663.2797613</v>
-      </c>
-      <c r="F7">
-        <v>-2823962686.52739</v>
+        <v>-3082640259.66852</v>
+      </c>
+      <c r="E7">
+        <v>-2952884634.466042</v>
       </c>
       <c r="H7">
-        <v>-2726076171.2936487</v>
-      </c>
-      <c r="I7">
-        <v>-3376886187.1430497</v>
+        <v>-3022018527.0957665</v>
+      </c>
+      <c r="J7">
+        <v>-2917266837.5637174</v>
+      </c>
+      <c r="K7">
+        <v>-3613720772.6314263</v>
       </c>
     </row>
     <row r="8">
@@ -3240,22 +3703,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>1386822695.0252657</v>
+        <v>1401075782.725047</v>
       </c>
       <c r="C8">
-        <v>1351019988.0252657</v>
+        <v>1484085675.725047</v>
       </c>
       <c r="D8">
-        <v>1300290469.7226634</v>
-      </c>
-      <c r="F8">
-        <v>1173643291.4358869</v>
+        <v>1445772443.725047</v>
+      </c>
+      <c r="E8">
+        <v>1391485060.6401005</v>
       </c>
       <c r="H8">
-        <v>1089080474.1767926</v>
-      </c>
-      <c r="I8">
-        <v>1028446759.0664762</v>
+        <v>1255955607.2896807</v>
+      </c>
+      <c r="J8">
+        <v>1165462060.1618874</v>
+      </c>
+      <c r="K8">
+        <v>1100575859.1847253</v>
       </c>
     </row>
     <row r="9">
@@ -3283,22 +3749,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>1386822695.0252657</v>
+        <v>1401075782.725047</v>
       </c>
       <c r="C13">
-        <v>1351019988.0252657</v>
+        <v>1484085675.725047</v>
       </c>
       <c r="D13">
-        <v>1300290469.7226634</v>
-      </c>
-      <c r="F13">
-        <v>1173643291.4358869</v>
+        <v>1445772443.725047</v>
+      </c>
+      <c r="E13">
+        <v>1391485060.6401005</v>
       </c>
       <c r="H13">
-        <v>1089080474.1767926</v>
-      </c>
-      <c r="I13">
-        <v>1028446759.0664762</v>
+        <v>1255955607.2896807</v>
+      </c>
+      <c r="J13">
+        <v>1165462060.1618874</v>
+      </c>
+      <c r="K13">
+        <v>1100575859.1847253</v>
       </c>
     </row>
     <row r="14"/>
@@ -3307,22 +3776,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-89794330.375381</v>
+        <v>-91145177.44993983</v>
       </c>
       <c r="C15">
-        <v>-85628280.375381</v>
+        <v>-96091913.44993983</v>
       </c>
       <c r="D15">
-        <v>-75822183.79910247</v>
-      </c>
-      <c r="F15">
-        <v>-66607246.59138215</v>
+        <v>-91633735.44993983</v>
+      </c>
+      <c r="E15">
+        <v>-81139897.95223369</v>
       </c>
       <c r="H15">
-        <v>-64932415.35791543</v>
-      </c>
-      <c r="I15">
-        <v>-26522580.604047257</v>
+        <v>-71278680.20293011</v>
+      </c>
+      <c r="J15">
+        <v>-69486386.33111589</v>
+      </c>
+      <c r="K15">
+        <v>-28382715.662006054</v>
       </c>
     </row>
     <row r="16">
@@ -3330,22 +3802,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-423850501.7505628</v>
+        <v>-480511518.1417412</v>
       </c>
       <c r="C16">
-        <v>-401067634.7505628</v>
+        <v>-453576544.1417412</v>
       </c>
       <c r="D16">
-        <v>-350427652.7014295</v>
-      </c>
-      <c r="F16">
-        <v>-332134455.80083495</v>
+        <v>-429196118.1417412</v>
+      </c>
+      <c r="E16">
+        <v>-375004550.84718037</v>
       </c>
       <c r="H16">
-        <v>-305956895.15302235</v>
-      </c>
-      <c r="I16">
-        <v>-379769862.59172255</v>
+        <v>-355428378.60625464</v>
+      </c>
+      <c r="J16">
+        <v>-327414880.53516555</v>
+      </c>
+      <c r="K16">
+        <v>-406404647.7172416</v>
       </c>
     </row>
     <row r="17">
@@ -3358,22 +3833,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>53816480.3780561</v>
+        <v>74040289.20208488</v>
       </c>
       <c r="C18">
-        <v>60615720.3780561</v>
+        <v>57590934.202084884</v>
       </c>
       <c r="D18">
-        <v>102945756.03093216</v>
-      </c>
-      <c r="F18">
-        <v>59248620.95823124</v>
+        <v>64866944.202084884</v>
+      </c>
+      <c r="E18">
+        <v>110165755.19767947</v>
       </c>
       <c r="H18">
-        <v>51690877.7880388</v>
-      </c>
-      <c r="I18">
-        <v>48084849.50740374</v>
+        <v>63403964.61145405</v>
+      </c>
+      <c r="J18">
+        <v>55316166.57066661</v>
+      </c>
+      <c r="K18">
+        <v>51457233.04958988</v>
       </c>
     </row>
     <row r="19">
@@ -3381,22 +3859,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-62392585.74686599</v>
+        <v>-55372947.93000026</v>
       </c>
       <c r="C19">
-        <v>-36145145.74686599</v>
+        <v>-66768088.93000026</v>
       </c>
       <c r="D19">
-        <v>-72830144.10196313</v>
-      </c>
-      <c r="F19">
-        <v>-90960583.35866153</v>
+        <v>-38680149.93000026</v>
+      </c>
+      <c r="E19">
+        <v>-77938014.49899304</v>
       </c>
       <c r="H19">
-        <v>-50865703.69917618</v>
-      </c>
-      <c r="I19">
-        <v>-35907304.49313083</v>
+        <v>-97340014.24903312</v>
+      </c>
+      <c r="J19">
+        <v>-54433119.71012587</v>
+      </c>
+      <c r="K19">
+        <v>-38425627.91427944</v>
       </c>
     </row>
     <row r="20">
@@ -3409,22 +3890,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>864601757.530512</v>
+        <v>848086428.4054506</v>
       </c>
       <c r="C21">
-        <v>888794647.530512</v>
+        <v>925240063.4054506</v>
       </c>
       <c r="D21">
-        <v>904156245.1511005</v>
-      </c>
-      <c r="F21">
-        <v>743189626.6432395</v>
+        <v>951129384.4054506</v>
+      </c>
+      <c r="E21">
+        <v>967568352.5393727</v>
       </c>
       <c r="H21">
-        <v>719016337.7547176</v>
-      </c>
-      <c r="I21">
-        <v>634331860.8849792</v>
+        <v>795312498.8429168</v>
+      </c>
+      <c r="J21">
+        <v>769443840.1561468</v>
+      </c>
+      <c r="K21">
+        <v>678820100.940788</v>
       </c>
     </row>
     <row r="22"/>
@@ -3443,19 +3927,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>24520426.72784992</v>
+        <v>45745251.41741157</v>
       </c>
       <c r="C25">
-        <v>3530721.7278499203</v>
+        <v>26239871.417411573</v>
       </c>
       <c r="D25">
-        <v>3268122.699776275</v>
-      </c>
-      <c r="F25">
-        <v>11481480.060002219</v>
+        <v>3778345.4174115723</v>
+      </c>
+      <c r="E25">
+        <v>3497329.2652428774</v>
       </c>
       <c r="H25">
-        <v>50925929.95289289</v>
+        <v>12286722.351304973</v>
+      </c>
+      <c r="J25">
+        <v>54497569.872806065</v>
       </c>
     </row>
     <row r="26">
@@ -3498,22 +3985,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>889122184.2583618</v>
+        <v>893831679.822862</v>
       </c>
       <c r="C33">
-        <v>892325369.2583618</v>
+        <v>951479934.822862</v>
       </c>
       <c r="D33">
-        <v>907424367.8508768</v>
-      </c>
-      <c r="F33">
-        <v>754671106.7032417</v>
+        <v>954907729.822862</v>
+      </c>
+      <c r="E33">
+        <v>971065681.8046156</v>
       </c>
       <c r="H33">
-        <v>769942267.7076104</v>
-      </c>
-      <c r="I33">
-        <v>634331860.8849792</v>
+        <v>807599221.1942219</v>
+      </c>
+      <c r="J33">
+        <v>823941410.0289527</v>
+      </c>
+      <c r="K33">
+        <v>678820100.940788</v>
       </c>
     </row>
     <row r="34"/>
@@ -3522,22 +4012,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>136855007.15434265</v>
+        <v>155621896.81259125</v>
       </c>
       <c r="C35">
-        <v>105864860.15434265</v>
+        <v>146452796.81259125</v>
       </c>
       <c r="D35">
-        <v>125237464.29799205</v>
-      </c>
-      <c r="F35">
-        <v>87146164.02506068</v>
+        <v>113289587.81259127</v>
+      </c>
+      <c r="E35">
+        <v>134020870.46002325</v>
       </c>
       <c r="H35">
-        <v>93820612.14818752</v>
-      </c>
-      <c r="I35">
-        <v>105550391.05443066</v>
+        <v>93258074.37381862</v>
+      </c>
+      <c r="J35">
+        <v>100400628.33972536</v>
+      </c>
+      <c r="K35">
+        <v>112953063.73220344</v>
       </c>
     </row>
     <row r="36">
@@ -3545,22 +4038,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-371225903.96267647</v>
+        <v>-455524840.8144866</v>
       </c>
       <c r="C36">
-        <v>-359595510.96267647</v>
+        <v>-397261316.8144866</v>
       </c>
       <c r="D36">
-        <v>-416904639.48078156</v>
-      </c>
-      <c r="F36">
-        <v>-302043944.3709699</v>
+        <v>-384815387.8144866</v>
+      </c>
+      <c r="E36">
+        <v>-446143835.59450877</v>
       </c>
       <c r="H36">
-        <v>-242100640.2450092</v>
-      </c>
-      <c r="I36">
-        <v>-342612778.93039954</v>
+        <v>-323227498.8054453</v>
+      </c>
+      <c r="J36">
+        <v>-259080130.10676464</v>
+      </c>
+      <c r="K36">
+        <v>-366641588.6042166</v>
       </c>
     </row>
     <row r="37">
@@ -3568,22 +4064,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-200477654.190266</v>
+        <v>-162119436.09804577</v>
       </c>
       <c r="C37">
-        <v>-155907557.190266</v>
+        <v>-214537380.09804577</v>
       </c>
       <c r="D37">
-        <v>-231507974.80867183</v>
-      </c>
-      <c r="F37">
-        <v>-217481439.2493974</v>
+        <v>-166841980.09804577</v>
+      </c>
+      <c r="E37">
+        <v>-247744558.51700595</v>
       </c>
       <c r="H37">
-        <v>-139529083.1528917</v>
-      </c>
-      <c r="I37">
-        <v>-49434952.94112057</v>
+        <v>-232734285.70663118</v>
+      </c>
+      <c r="J37">
+        <v>-149314817.92177525</v>
+      </c>
+      <c r="K37">
+        <v>-52902024.65737315</v>
       </c>
     </row>
     <row r="38">
@@ -3591,22 +4090,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>454273633.25976205</v>
+        <v>431809299.72292095</v>
       </c>
       <c r="C38">
-        <v>482687161.25976205</v>
+        <v>486134034.72292095</v>
       </c>
       <c r="D38">
-        <v>384249217.85941553</v>
-      </c>
-      <c r="F38">
-        <v>322291887.10793513</v>
+        <v>516539949.72292095</v>
+      </c>
+      <c r="E38">
+        <v>411198158.1531242</v>
       </c>
       <c r="H38">
-        <v>482133156.45789707</v>
-      </c>
-      <c r="I38">
-        <v>347834520.06788987</v>
+        <v>344895511.055964</v>
+      </c>
+      <c r="J38">
+        <v>515947090.34013826</v>
+      </c>
+      <c r="K38">
+        <v>372229551.4114018</v>
       </c>
     </row>
     <row r="39"/>
@@ -3615,22 +4117,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>50588663.914473206</v>
+        <v>82289644.9380683</v>
       </c>
       <c r="C40">
-        <v>61938276.91447321</v>
+        <v>54136796.9380683</v>
       </c>
       <c r="D40">
-        <v>60321747.9869397</v>
-      </c>
-      <c r="F40">
-        <v>-72538881.2346615</v>
+        <v>66282256.93806829</v>
+      </c>
+      <c r="E40">
+        <v>64552354.34696862</v>
       </c>
       <c r="H40">
-        <v>-178194863.98235932</v>
-      </c>
-      <c r="I40">
-        <v>-41428449.78397016</v>
+        <v>-77626324.1974746</v>
+      </c>
+      <c r="J40">
+        <v>-190692385.19231296</v>
+      </c>
+      <c r="K40">
+        <v>-44333993.2901058</v>
       </c>
     </row>
     <row r="41">
@@ -3638,22 +4143,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-116752722.98290488</v>
+        <v>-118749033.65517507</v>
       </c>
       <c r="C41">
-        <v>-116800794.98290488</v>
+        <v>-124941060.65517507</v>
       </c>
       <c r="D41">
-        <v>-96151449.0187452</v>
-      </c>
-      <c r="F41">
-        <v>-72661262.47119558</v>
+        <v>-124992503.65517507</v>
+      </c>
+      <c r="E41">
+        <v>-102894936.15762538</v>
       </c>
       <c r="H41">
-        <v>-133778677.09484382</v>
-      </c>
-      <c r="I41">
-        <v>-52503256.98465203</v>
+        <v>-77757288.52145073</v>
+      </c>
+      <c r="J41">
+        <v>-143161112.80072287</v>
+      </c>
+      <c r="K41">
+        <v>-56185521.18179686</v>
       </c>
     </row>
     <row r="42">
@@ -3661,22 +4169,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>167341386.89737812</v>
+        <v>201038678.5932434</v>
       </c>
       <c r="C42">
-        <v>178739071.89737812</v>
+        <v>179077857.5932434</v>
       </c>
       <c r="D42">
-        <v>156473197.00568485</v>
-      </c>
-      <c r="F42">
-        <v>122381.2365340778</v>
+        <v>191274760.5932434</v>
+      </c>
+      <c r="E42">
+        <v>167447290.50459397</v>
       </c>
       <c r="H42">
-        <v>44416186.887515515</v>
-      </c>
-      <c r="I42">
-        <v>11074807.200681867</v>
+        <v>130964.3239761289</v>
+      </c>
+      <c r="J42">
+        <v>47531272.391590096</v>
+      </c>
+      <c r="K42">
+        <v>11851527.891691068</v>
       </c>
     </row>
     <row r="43">
@@ -3684,22 +4195,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>504862297.1742352</v>
+        <v>514098944.66098917</v>
       </c>
       <c r="C43">
-        <v>544625438.1742352</v>
+        <v>540270831.6609892</v>
       </c>
       <c r="D43">
-        <v>444570965.8463553</v>
-      </c>
-      <c r="F43">
-        <v>249753005.87327364</v>
+        <v>582822206.6609892</v>
+      </c>
+      <c r="E43">
+        <v>475750512.5000929</v>
       </c>
       <c r="H43">
-        <v>303938292.47553766</v>
-      </c>
-      <c r="I43">
-        <v>306406070.28391963</v>
+        <v>267269186.85848942</v>
+      </c>
+      <c r="J43">
+        <v>325254705.14782524</v>
+      </c>
+      <c r="K43">
+        <v>327895558.1212959</v>
       </c>
     </row>
     <row r="44">
@@ -3713,22 +4227,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>504862297.1742352</v>
+        <v>514098944.66098917</v>
       </c>
       <c r="C46">
-        <v>544625438.1742352</v>
+        <v>540270831.6609892</v>
       </c>
       <c r="D46">
-        <v>444570965.8463553</v>
-      </c>
-      <c r="F46">
-        <v>249753005.87327364</v>
+        <v>582822206.6609892</v>
+      </c>
+      <c r="E46">
+        <v>475750512.5000929</v>
       </c>
       <c r="H46">
-        <v>303938292.47553766</v>
-      </c>
-      <c r="I46">
-        <v>306406070.28391963</v>
+        <v>267269186.85848942</v>
+      </c>
+      <c r="J46">
+        <v>325254705.14782524</v>
+      </c>
+      <c r="K46">
+        <v>327895558.1212959</v>
       </c>
     </row>
     <row r="47">
@@ -3736,22 +4253,25 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>558813.4506114341</v>
+        <v>641536.6126578389</v>
       </c>
       <c r="C47">
-        <v>874385.4506114341</v>
+        <v>598010.6126578389</v>
       </c>
       <c r="D47">
-        <v>551797.0938514671</v>
-      </c>
-      <c r="F47">
-        <v>281446.1422534129</v>
+        <v>935709.6126578389</v>
+      </c>
+      <c r="E47">
+        <v>590496.8393429094</v>
       </c>
       <c r="H47">
-        <v>898389.3056230361</v>
-      </c>
-      <c r="I47">
-        <v>265231.61668082274</v>
+        <v>301185.09013139363</v>
+      </c>
+      <c r="J47">
+        <v>961396.9543896746</v>
+      </c>
+      <c r="K47">
+        <v>283833.37478394643</v>
       </c>
     </row>
     <row r="48">
@@ -3759,22 +4279,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>504303483.72362375</v>
+        <v>513457408.0483314</v>
       </c>
       <c r="C48">
-        <v>543751052.7236238</v>
+        <v>539672821.0483314</v>
       </c>
       <c r="D48">
-        <v>444019168.7525038</v>
-      </c>
-      <c r="F48">
-        <v>249471559.7310202</v>
+        <v>581886497.0483314</v>
+      </c>
+      <c r="E48">
+        <v>475160015.66075</v>
       </c>
       <c r="H48">
-        <v>303039903.1699146</v>
-      </c>
-      <c r="I48">
-        <v>306140838.66723883</v>
+        <v>266968001.768358</v>
+      </c>
+      <c r="J48">
+        <v>324293308.19343555</v>
+      </c>
+      <c r="K48">
+        <v>327611724.746512</v>
       </c>
     </row>
     <row r="49"/>
@@ -3783,34 +4306,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>138800212.28227282</v>
+        <v>171150797.3925672</v>
       </c>
       <c r="C50">
-        <v>145881911.28227282</v>
+        <v>148534828.4108022</v>
       </c>
       <c r="D50">
-        <v>150998525.85001534</v>
-      </c>
-      <c r="F50">
-        <v>103724450.1488672</v>
+        <v>156113195.3925672</v>
+      </c>
+      <c r="E50">
+        <v>161588658.68161654</v>
       </c>
       <c r="H50">
-        <v>107375616.53973901</v>
-      </c>
-      <c r="I50">
-        <v>64584697.911915466</v>
+        <v>110999062.26032837</v>
+      </c>
+      <c r="J50">
+        <v>114906299.60852872</v>
+      </c>
+      <c r="K50">
+        <v>69114282.06464681</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3821,6 +4347,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3828,27 +4356,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3862,28 +4396,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-36442646</v>
+        <v>-44169628</v>
       </c>
       <c r="C3">
-        <v>256346592.79326212</v>
+        <v>-38998515.07026074</v>
       </c>
       <c r="D3">
-        <v>344525756.5684749</v>
+        <v>274325208.5004482</v>
       </c>
       <c r="E3">
-        <v>24199355</v>
+        <v>368688731.0440809</v>
       </c>
       <c r="F3">
-        <v>-111615397.24178185</v>
+        <v>126855489</v>
       </c>
       <c r="G3">
-        <v>-166247322.71638322</v>
+        <v>25896552.919293776</v>
       </c>
       <c r="H3">
-        <v>500959246.4959997</v>
+        <v>-119443433.15265222</v>
       </c>
       <c r="I3">
-        <v>-455990857.00111663</v>
+        <v>-177906914.89156336</v>
+      </c>
+      <c r="J3">
+        <v>536093529.6537115</v>
+      </c>
+      <c r="K3">
+        <v>-487971326.4689715</v>
       </c>
     </row>
     <row r="4">
@@ -3891,28 +4431,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>4586945</v>
+        <v>92365950</v>
       </c>
       <c r="C4">
-        <v>544625438.1742352</v>
+        <v>4908645.868056813</v>
       </c>
       <c r="D4">
-        <v>317426589.3378514</v>
+        <v>582822206.6609892</v>
       </c>
       <c r="E4">
-        <v>44350086</v>
+        <v>339688990.4205547</v>
       </c>
       <c r="F4">
-        <v>249753005.87327364</v>
+        <v>159691022</v>
       </c>
       <c r="G4">
-        <v>122608629.36476976</v>
+        <v>47460535.58345791</v>
       </c>
       <c r="H4">
-        <v>303938292.47553766</v>
+        <v>267269186.85848942</v>
       </c>
       <c r="I4">
-        <v>306406070.28391963</v>
+        <v>131207664.77895121</v>
+      </c>
+      <c r="J4">
+        <v>325254705.14782524</v>
+      </c>
+      <c r="K4">
+        <v>327895558.1212959</v>
       </c>
     </row>
     <row r="5">
@@ -3920,28 +4466,34 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>13646490</v>
+        <v>-8274631</v>
       </c>
       <c r="C5">
-        <v>-127697727.5530398</v>
+        <v>14603573.130259601</v>
       </c>
       <c r="D5">
-        <v>-155590228.21096334</v>
+        <v>-136653681.8543657</v>
       </c>
       <c r="E5">
-        <v>21511056</v>
+        <v>-166502395.56344405</v>
       </c>
       <c r="F5">
-        <v>63179111.70837851</v>
+        <v>421589</v>
       </c>
       <c r="G5">
-        <v>118132646.02074708</v>
+        <v>23019712.71771053</v>
       </c>
       <c r="H5">
-        <v>-54297633.25210114</v>
+        <v>67610116.45764926</v>
       </c>
       <c r="I5">
-        <v>-233478545.67667097</v>
+        <v>126417762.75328314</v>
+      </c>
+      <c r="J5">
+        <v>-58105744.26076408</v>
+      </c>
+      <c r="K5">
+        <v>-249853333.43122816</v>
       </c>
     </row>
     <row r="6">
@@ -3949,28 +4501,34 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>28565000</v>
+        <v>77801908</v>
       </c>
       <c r="C6">
-        <v>145881911.28227282</v>
+        <v>30568378.129897542</v>
       </c>
       <c r="D6">
-        <v>104456041.92221476</v>
+        <v>156113195.3925672</v>
       </c>
       <c r="E6">
-        <v>35646699</v>
+        <v>111781963.50186208</v>
       </c>
       <c r="F6">
-        <v>103724450.1488672</v>
+        <v>62764306</v>
       </c>
       <c r="G6">
-        <v>57181966.22106663</v>
+        <v>38146745.111662544</v>
       </c>
       <c r="H6">
-        <v>107375616.53973901</v>
+        <v>110999062.26032837</v>
       </c>
       <c r="I6">
-        <v>64584697.911915466</v>
+        <v>61192367.08057389</v>
+      </c>
+      <c r="J6">
+        <v>114906299.60852872</v>
+      </c>
+      <c r="K6">
+        <v>69114282.06464681</v>
       </c>
     </row>
     <row r="7">
@@ -3978,28 +4536,34 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>6755364</v>
+        <v>3909306</v>
       </c>
       <c r="C7">
-        <v>6371102.491156474</v>
+        <v>7229144.798077969</v>
       </c>
       <c r="D7">
-        <v>4614361.562101674</v>
+        <v>6817933.486924673</v>
       </c>
       <c r="E7">
-        <v>837001</v>
+        <v>4937985.2637279425</v>
       </c>
       <c r="F7">
-        <v>18021320.166625403</v>
+        <v>1389284</v>
       </c>
       <c r="G7">
-        <v>17044451.245508164</v>
+        <v>895703.2404376814</v>
       </c>
       <c r="H7">
-        <v>2217751.466182786</v>
+        <v>19285227.700099893</v>
       </c>
       <c r="I7">
-        <v>12069913.811090454</v>
+        <v>18239847.03970932</v>
+      </c>
+      <c r="J7">
+        <v>2373291.2801123783</v>
+      </c>
+      <c r="K7">
+        <v>12916425.323741842</v>
       </c>
     </row>
     <row r="8">
@@ -4007,28 +4571,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>7359269</v>
+        <v>2542019</v>
       </c>
       <c r="C8">
-        <v>14855379.542253982</v>
+        <v>7875404.080225204</v>
       </c>
       <c r="D8">
-        <v>15805522.816578662</v>
+        <v>15897246.949440364</v>
       </c>
       <c r="E8">
-        <v>9209263</v>
+        <v>16914027.586133372</v>
       </c>
       <c r="F8">
-        <v>7842196.195619076</v>
+        <v>8826605</v>
       </c>
       <c r="G8">
-        <v>8622255.337043615</v>
+        <v>9855145.5866156</v>
       </c>
       <c r="H8">
-        <v>4186059.950897179</v>
+        <v>8392200.898880722</v>
       </c>
       <c r="I8">
-        <v>9714401.937996328</v>
+        <v>9226968.719596583</v>
+      </c>
+      <c r="J8">
+        <v>4479645.141027316</v>
+      </c>
+      <c r="K8">
+        <v>10395711.946314763</v>
       </c>
     </row>
     <row r="9">
@@ -4051,28 +4621,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>438724</v>
+        <v>3428167</v>
       </c>
       <c r="C12">
-        <v>-12688133.544445299</v>
+        <v>469493.4754651206</v>
       </c>
       <c r="D12">
-        <v>-21746149.25843871</v>
+        <v>-13578003.288963452</v>
       </c>
       <c r="E12">
-        <v>-31359018</v>
+        <v>-23271294.010192387</v>
       </c>
       <c r="F12">
-        <v>18937511.751026645</v>
+        <v>-26962247</v>
       </c>
       <c r="G12">
-        <v>66273322.82168673</v>
+        <v>-33558351.829380825</v>
       </c>
       <c r="H12">
-        <v>-11963242.626748476</v>
+        <v>20265675.478549294</v>
       </c>
       <c r="I12">
-        <v>-4774000.2931142</v>
+        <v>70921337.01866229</v>
+      </c>
+      <c r="J12">
+        <v>-12802272.860989187</v>
+      </c>
+      <c r="K12">
+        <v>-5108820.099847945</v>
       </c>
     </row>
     <row r="13">
@@ -4115,28 +4691,34 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>42490621</v>
+        <v>-40881212</v>
       </c>
       <c r="C20">
-        <v>-178051018.71025962</v>
+        <v>45470658.83781429</v>
       </c>
       <c r="D20">
-        <v>-175510085.16889897</v>
+        <v>-190538451.47378534</v>
       </c>
       <c r="E20">
-        <v>30090094</v>
+        <v>-187819312.06208387</v>
       </c>
       <c r="F20">
-        <v>-826813.1053226215</v>
+        <v>-30536022</v>
       </c>
       <c r="G20">
-        <v>-17911612.37846651</v>
+        <v>32200433.094911996</v>
       </c>
       <c r="H20">
-        <v>45040931.77977679</v>
+        <v>-884800.8278052405</v>
       </c>
       <c r="I20">
-        <v>-7724343.744145022</v>
+        <v>-19167825.664313592</v>
+      </c>
+      <c r="J20">
+        <v>48199833.151308805</v>
+      </c>
+      <c r="K20">
+        <v>-8266082.98184259</v>
       </c>
     </row>
     <row r="21">
@@ -4148,8 +4730,8 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="H22">
-        <v>53728454.617797464</v>
+      <c r="J22">
+        <v>57496646.84375539</v>
       </c>
     </row>
     <row r="23">
@@ -4182,22 +4764,31 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-28504960</v>
+        <v>-111097479</v>
       </c>
       <c r="C28">
-        <v>-184555764.1571259</v>
-      </c>
-      <c r="E28">
-        <v>-51154061</v>
+        <v>-30504127.28365497</v>
+      </c>
+      <c r="D28">
+        <v>-197499400.83344007</v>
       </c>
       <c r="F28">
-        <v>-390152316.32895356</v>
+        <v>-51754007</v>
+      </c>
+      <c r="G28">
+        <v>-54741700.66612444</v>
+      </c>
+      <c r="H28">
+        <v>-417515264.61749876</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
+      <c r="B29">
+        <v>-65488080</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -4209,28 +4800,34 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-90409013</v>
+        <v>-186942482</v>
       </c>
       <c r="C31">
-        <v>-420128081.2504105</v>
+        <v>-96749760.0467293</v>
       </c>
       <c r="D31">
-        <v>-484853152.8046104</v>
+        <v>-449593350.2765925</v>
       </c>
       <c r="E31">
-        <v>-280057527</v>
+        <v>-518857850.95061517</v>
       </c>
       <c r="F31">
-        <v>-216910242.07974115</v>
+        <v>-315562571</v>
       </c>
       <c r="G31">
-        <v>497387247.2085459</v>
+        <v>-299699085.7153856</v>
       </c>
       <c r="H31">
-        <v>-226714300.0089985</v>
+        <v>-232123028.18628183</v>
       </c>
       <c r="I31">
-        <v>-342975297.432422</v>
+        <v>532271011.71572405</v>
+      </c>
+      <c r="J31">
+        <v>-242614684.05846664</v>
+      </c>
+      <c r="K31">
+        <v>-367029531.9841888</v>
       </c>
     </row>
     <row r="32">
@@ -4243,28 +4840,34 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>119519209</v>
+        <v>73236980</v>
       </c>
       <c r="C33">
-        <v>-54119797.01469889</v>
+        <v>127901570.96090508</v>
       </c>
       <c r="D33">
-        <v>-328921898.5708329</v>
+        <v>-57915435.65407372</v>
       </c>
       <c r="E33">
-        <v>-50835655</v>
+        <v>-351990511.84025997</v>
       </c>
       <c r="F33">
-        <v>-87863748.13809276</v>
+        <v>-110072758</v>
       </c>
       <c r="G33">
-        <v>-47521502.183712386</v>
+        <v>-54400963.57503996</v>
       </c>
       <c r="H33">
-        <v>-328113883.0962218</v>
+        <v>-94025985.54158238</v>
       </c>
       <c r="I33">
-        <v>-216076531.05030856</v>
+        <v>-50854375.91641771</v>
+      </c>
+      <c r="J33">
+        <v>-351125826.99647486</v>
+      </c>
+      <c r="K33">
+        <v>-231230845.6552557</v>
       </c>
     </row>
     <row r="34">
@@ -4287,28 +4890,34 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-96474000</v>
+        <v>-66099879</v>
       </c>
       <c r="C37">
-        <v>-66735887.028489955</v>
+        <v>-103240108.93414092</v>
       </c>
       <c r="D37">
-        <v>82431782.32544947</v>
+        <v>-71416342.71034501</v>
       </c>
       <c r="E37">
-        <v>107803364</v>
+        <v>88213054.15878677</v>
       </c>
       <c r="F37">
-        <v>-16874056.459777966</v>
+        <v>97747911</v>
       </c>
       <c r="G37">
-        <v>128911126.64043929</v>
+        <v>115364046.71545541</v>
       </c>
       <c r="H37">
-        <v>17155434.476196982</v>
+        <v>-18057501.783571962</v>
       </c>
       <c r="I37">
-        <v>-109445314.95682493</v>
+        <v>137952181.4911975</v>
+      </c>
+      <c r="J37">
+        <v>18358613.969930686</v>
+      </c>
+      <c r="K37">
+        <v>-117121154.28482252</v>
       </c>
     </row>
     <row r="38">
@@ -4321,28 +4930,34 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-26379485</v>
+        <v>45631349</v>
       </c>
       <c r="C39">
-        <v>79967089.8547812</v>
+        <v>-28229584.188761078</v>
       </c>
       <c r="D39">
-        <v>37264944.53408449</v>
+        <v>85575502.91015036</v>
       </c>
       <c r="E39">
-        <v>-27500122</v>
+        <v>39878484.70182227</v>
       </c>
       <c r="F39">
-        <v>-152833767.0080965</v>
+        <v>9895568</v>
       </c>
       <c r="G39">
-        <v>131968475.44504961</v>
+        <v>-29428815.960592132</v>
       </c>
       <c r="H39">
-        <v>-5131640.613277422</v>
+        <v>-163552612.6700561</v>
       </c>
       <c r="I39">
-        <v>-3514919.5069701415</v>
+        <v>141223954.44181255</v>
+      </c>
+      <c r="J39">
+        <v>-5491543.171482708</v>
+      </c>
+      <c r="K39">
+        <v>-3761434.923340323</v>
       </c>
     </row>
     <row r="40">
@@ -4350,28 +4965,34 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>55422338</v>
+        <v>87022437</v>
       </c>
       <c r="C40">
-        <v>264327279.3036851</v>
+        <v>59309329.06798492</v>
       </c>
       <c r="D40">
-        <v>83139166.92564787</v>
+        <v>282865612.5959071</v>
       </c>
       <c r="E40">
-        <v>159352655</v>
+        <v>88970050.48093385</v>
       </c>
       <c r="F40">
-        <v>65599493.29057136</v>
+        <v>234295778</v>
       </c>
       <c r="G40">
-        <v>149434047.682373</v>
+        <v>170528696.4482096</v>
       </c>
       <c r="H40">
-        <v>133920061.68771271</v>
+        <v>70200249.11730656</v>
       </c>
       <c r="I40">
-        <v>2211190.954656957</v>
+        <v>159914457.3791674</v>
+      </c>
+      <c r="J40">
+        <v>143312413.26270634</v>
+      </c>
+      <c r="K40">
+        <v>2366270.653574759</v>
       </c>
     </row>
     <row r="41">
@@ -4384,28 +5005,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>19536665</v>
+        <v>13883733</v>
       </c>
       <c r="C42">
-        <v>13575565.598784246</v>
+        <v>20906849.75029353</v>
       </c>
       <c r="D42">
-        <v>9971380.378353657</v>
+        <v>14527674.516046412</v>
       </c>
       <c r="E42">
-        <v>11072667</v>
+        <v>10670713.316385625</v>
       </c>
       <c r="F42">
-        <v>524889.2092934571</v>
+        <v>9478531</v>
       </c>
       <c r="G42">
-        <v>6808314.666502337</v>
+        <v>11849237.59014312</v>
       </c>
       <c r="H42">
-        <v>2679766.274897393</v>
+        <v>561701.7968137695</v>
       </c>
       <c r="I42">
-        <v>5207655.502206568</v>
+        <v>7285809.1074031405</v>
+      </c>
+      <c r="J42">
+        <v>2867709.042212864</v>
+      </c>
+      <c r="K42">
+        <v>5572889.289749408</v>
       </c>
     </row>
     <row r="43">
@@ -4418,28 +5045,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>22086197</v>
+        <v>25880694</v>
       </c>
       <c r="C44">
-        <v>23761053.31045827</v>
+        <v>23635190.66505894</v>
       </c>
       <c r="D44">
-        <v>35744634.12367472</v>
+        <v>25427511.372614812</v>
       </c>
       <c r="E44">
-        <v>32048629</v>
+        <v>38251548.81874069</v>
       </c>
       <c r="F44">
-        <v>885489.8094351812</v>
+        <v>22204363</v>
       </c>
       <c r="G44">
-        <v>23248305.436971746</v>
+        <v>34296328.01739191</v>
       </c>
       <c r="H44">
-        <v>13242287.441052264</v>
+        <v>947592.7647465616</v>
       </c>
       <c r="I44">
-        <v>3584920.4979716204</v>
+        <v>24878802.432231937</v>
+      </c>
+      <c r="J44">
+        <v>14171022.223100958</v>
+      </c>
+      <c r="K44">
+        <v>3836345.3648736943</v>
       </c>
     </row>
     <row r="45">
@@ -4457,28 +5090,34 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-4179610</v>
+        <v>-21036142</v>
       </c>
       <c r="C47">
-        <v>-7181036.222780012</v>
+        <v>-4472742.829179103</v>
       </c>
       <c r="D47">
-        <v>-3746253.0421297094</v>
+        <v>-7684671.122787696</v>
       </c>
       <c r="E47">
-        <v>-6312708</v>
+        <v>-4008992.8080553105</v>
       </c>
       <c r="F47">
-        <v>38939403.42071278</v>
+        <v>-8895126</v>
       </c>
       <c r="G47">
-        <v>10413534.510219112</v>
+        <v>-6755443.555667048</v>
       </c>
       <c r="H47">
-        <v>78836011.0882152</v>
+        <v>41670380.11261943</v>
       </c>
       <c r="I47">
-        <v>76178374.62560807</v>
+        <v>11143877.492634876</v>
+      </c>
+      <c r="J47">
+        <v>84365097.04874349</v>
+      </c>
+      <c r="K47">
+        <v>81521069.87140135</v>
       </c>
     </row>
     <row r="48">
@@ -4486,28 +5125,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-27627261</v>
+        <v>-17186089</v>
       </c>
       <c r="C48">
-        <v>-18021950.70845535</v>
+        <v>-29564871.72908704</v>
       </c>
       <c r="D48">
-        <v>3323963.032157091</v>
+        <v>-19285902.464359812</v>
       </c>
       <c r="E48">
-        <v>3274636</v>
+        <v>3557085.904315727</v>
       </c>
       <c r="F48">
-        <v>-21619778.373257976</v>
+        <v>9154297</v>
       </c>
       <c r="G48">
-        <v>-2977326.1815266004</v>
+        <v>3504299.369360237</v>
       </c>
       <c r="H48">
-        <v>31578164.987871297</v>
+        <v>-23136060.22749277</v>
       </c>
       <c r="I48">
-        <v>32224083.118626047</v>
+        <v>-3186138.0197076523</v>
+      </c>
+      <c r="J48">
+        <v>33792868.47532089</v>
+      </c>
+      <c r="K48">
+        <v>34484087.437752806</v>
       </c>
     </row>
     <row r="49">
@@ -4515,16 +5160,22 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-10271525</v>
+        <v>-27006160</v>
       </c>
       <c r="C49">
-        <v>232371946.46406952</v>
-      </c>
-      <c r="E49">
-        <v>14707081</v>
+        <v>-10991908.285338555</v>
+      </c>
+      <c r="D49">
+        <v>248669123.97318342</v>
       </c>
       <c r="F49">
-        <v>-77220198.74730141</v>
+        <v>108358604</v>
+      </c>
+      <c r="G49">
+        <v>15738547.635043994</v>
+      </c>
+      <c r="H49">
+        <v>-82635961.30136006</v>
       </c>
     </row>
     <row r="50">
@@ -4552,28 +5203,34 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-26171121</v>
+        <v>-17163468</v>
       </c>
       <c r="C54">
-        <v>23974646.3291926</v>
+        <v>-28006606.784922186</v>
       </c>
       <c r="D54">
-        <v>-33797284.136397384</v>
+        <v>25656084.527264815</v>
       </c>
       <c r="E54">
-        <v>9492274</v>
+        <v>-36167623.35883014</v>
       </c>
       <c r="F54">
-        <v>-34395198.494480446</v>
+        <v>18496885</v>
       </c>
       <c r="G54">
-        <v>-19043584.832776</v>
+        <v>10158005.284249783</v>
       </c>
       <c r="H54">
-        <v>-35310941.01910181</v>
+        <v>-36807471.85129217</v>
       </c>
       <c r="I54">
-        <v>-10956428.609547343</v>
+        <v>-20379187.891373303</v>
+      </c>
+      <c r="J54">
+        <v>-37787439.0755965</v>
+      </c>
+      <c r="K54">
+        <v>-11724846.934705785</v>
       </c>
     </row>
     <row r="55">
@@ -4637,28 +5294,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-100268926</v>
+        <v>-336838581</v>
       </c>
       <c r="C67">
-        <v>-1268707176.9225612</v>
+        <v>-107301188.33000927</v>
       </c>
       <c r="D67">
-        <v>-870298450.4136884</v>
+        <v>-1357686704.7184901</v>
       </c>
       <c r="E67">
-        <v>-85654993</v>
+        <v>-931335974.7281468</v>
       </c>
       <c r="F67">
-        <v>-228133822.82834026</v>
+        <v>-381606574</v>
       </c>
       <c r="G67">
-        <v>-59178242.71877097</v>
+        <v>-91662321.53816652</v>
       </c>
       <c r="H67">
-        <v>-68305830.84383556</v>
+        <v>-244133763.7120867</v>
       </c>
       <c r="I67">
-        <v>-82218608.76390612</v>
+        <v>-63328650.463512935</v>
+      </c>
+      <c r="J67">
+        <v>-73096392.98831381</v>
+      </c>
+      <c r="K67">
+        <v>-87984929.87954456</v>
       </c>
     </row>
     <row r="68">
@@ -4711,28 +5374,34 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>3805030</v>
+        <v>2997472</v>
       </c>
       <c r="C77">
-        <v>6091216.747358326</v>
+        <v>4071892.029952881</v>
       </c>
       <c r="D77">
-        <v>10169825.229791936</v>
+        <v>6518418.232256744</v>
       </c>
       <c r="E77">
-        <v>2550135</v>
+        <v>10883075.90195176</v>
       </c>
       <c r="F77">
-        <v>20180991.959520414</v>
+        <v>1686491</v>
       </c>
       <c r="G77">
-        <v>3102836.013090918</v>
+        <v>2728986.205576274</v>
       </c>
       <c r="H77">
-        <v>9392636.006082168</v>
+        <v>21596365.94626438</v>
       </c>
       <c r="I77">
-        <v>3968821.23780448</v>
+        <v>3320450.359643861</v>
+      </c>
+      <c r="J77">
+        <v>10051379.277801868</v>
+      </c>
+      <c r="K77">
+        <v>4247170.604837226</v>
       </c>
     </row>
     <row r="78">
@@ -4740,28 +5409,34 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-104073956</v>
+        <v>-339836053</v>
       </c>
       <c r="C78">
-        <v>-1274798393.6699195</v>
+        <v>-111373080.35996215</v>
       </c>
       <c r="D78">
-        <v>-868984796.6905162</v>
+        <v>-1364205122.9507468</v>
       </c>
       <c r="E78">
-        <v>-88205128</v>
+        <v>-929930189.1954433</v>
       </c>
       <c r="F78">
-        <v>-248314814.7878607</v>
+        <v>-383293065</v>
       </c>
       <c r="G78">
-        <v>-62281078.73186189</v>
+        <v>-94391307.74374281</v>
       </c>
       <c r="H78">
-        <v>-137598348.6113114</v>
+        <v>-265730129.6583511</v>
       </c>
       <c r="I78">
-        <v>-109059309.29529998</v>
+        <v>-66649100.8231568</v>
+      </c>
+      <c r="J78">
+        <v>-147248673.21547452</v>
+      </c>
+      <c r="K78">
+        <v>-116708076.49655801</v>
       </c>
     </row>
     <row r="79">
@@ -4863,11 +5538,11 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="H98">
-        <v>-59486476.519086964</v>
-      </c>
-      <c r="I98">
-        <v>-12847481.989605669</v>
+      <c r="J98">
+        <v>-63658501.93771124</v>
+      </c>
+      <c r="K98">
+        <v>-13748527.480319079</v>
       </c>
     </row>
     <row r="99">
@@ -4881,28 +5556,34 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>794861788</v>
+        <v>772246132</v>
       </c>
       <c r="C101">
-        <v>1012767882.2392063</v>
+        <v>850608636.3238388</v>
       </c>
       <c r="D101">
-        <v>558084989.6041126</v>
+        <v>1083797359.7795765</v>
       </c>
       <c r="E101">
-        <v>66936400</v>
+        <v>597225730.4687012</v>
       </c>
       <c r="F101">
-        <v>220600639.4475436</v>
+        <v>261162377</v>
       </c>
       <c r="G101">
-        <v>201068004.16193774</v>
+        <v>71630918.46154644</v>
       </c>
       <c r="H101">
-        <v>-204287180.44864902</v>
+        <v>236072247.93732554</v>
       </c>
       <c r="I101">
-        <v>659854700.1465125</v>
+        <v>215169710.52147472</v>
+      </c>
+      <c r="J101">
+        <v>-218614660.5651992</v>
+      </c>
+      <c r="K101">
+        <v>706132959.3862683</v>
       </c>
     </row>
     <row r="102">
@@ -4920,9 +5601,12 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>912520327</v>
-      </c>
-      <c r="E104">
+        <v>976507241</v>
+      </c>
+      <c r="C104">
+        <v>976519041.0276126</v>
+      </c>
+      <c r="G104">
         <v>0</v>
       </c>
     </row>
@@ -4935,16 +5619,16 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="H106">
-        <v>-163825756.72400376</v>
+      <c r="J106">
+        <v>-175315514.754278</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="H107">
-        <v>100359014.5319878</v>
+      <c r="J107">
+        <v>107397595.13242379</v>
       </c>
     </row>
     <row r="108">
@@ -4960,13 +5644,19 @@
         <v>0</v>
       </c>
       <c r="C109">
-        <v>1012767882.2392063</v>
-      </c>
-      <c r="E109">
-        <v>66936400</v>
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>1083797359.7795765</v>
       </c>
       <c r="F109">
-        <v>220600639.4475436</v>
+        <v>261162377</v>
+      </c>
+      <c r="G109">
+        <v>71630918.46154644</v>
+      </c>
+      <c r="H109">
+        <v>236072247.93732554</v>
       </c>
     </row>
     <row r="110">
@@ -4974,19 +5664,22 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-117658539</v>
-      </c>
-      <c r="D110">
-        <v>558084989.6041126</v>
+        <v>-204261109</v>
+      </c>
+      <c r="C110">
+        <v>-125910404.70377374</v>
       </c>
       <c r="E110">
+        <v>597225730.4687012</v>
+      </c>
+      <c r="G110">
         <v>0</v>
       </c>
-      <c r="G110">
-        <v>201068004.16193774</v>
-      </c>
-      <c r="H110">
-        <v>-140821177.79267764</v>
+      <c r="I110">
+        <v>215169710.52147472</v>
+      </c>
+      <c r="J110">
+        <v>-150697532.34602138</v>
       </c>
     </row>
     <row r="111">
@@ -5064,28 +5757,34 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>658150216</v>
+        <v>391237923</v>
       </c>
       <c r="C125">
-        <v>407298.10990731016</v>
+        <v>704308932.9235688</v>
       </c>
       <c r="D125">
-        <v>32312295.758899033</v>
+        <v>435863.5615347182</v>
       </c>
       <c r="E125">
-        <v>5480762</v>
+        <v>34578486.7846354</v>
       </c>
       <c r="F125">
-        <v>-119148580.62257853</v>
+        <v>6411292</v>
       </c>
       <c r="G125">
-        <v>24357561.27321648</v>
+        <v>5865149.842673674</v>
       </c>
       <c r="H125">
-        <v>227952829.96120834</v>
+        <v>-127504948.92741339</v>
       </c>
       <c r="I125">
-        <v>121645234.38148978</v>
+        <v>26065854.833601605</v>
+      </c>
+      <c r="J125">
+        <v>243940077.0885508</v>
+      </c>
+      <c r="K125">
+        <v>130176703.03775224</v>
       </c>
     </row>
     <row r="126">
@@ -5093,9 +5792,15 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>-25030334</v>
+      </c>
+      <c r="C126">
         <v>0</v>
       </c>
-      <c r="E126">
+      <c r="F126">
+        <v>-12129839</v>
+      </c>
+      <c r="G126">
         <v>0</v>
       </c>
     </row>
@@ -5104,28 +5809,34 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>658150216</v>
+        <v>366207589</v>
       </c>
       <c r="C127">
-        <v>407298.10990731016</v>
+        <v>704308932.9235688</v>
       </c>
       <c r="D127">
-        <v>12978575.088636916</v>
+        <v>435863.5615347182</v>
       </c>
       <c r="E127">
-        <v>5480762</v>
+        <v>13888814.664684815</v>
       </c>
       <c r="F127">
-        <v>-119148580.62257853</v>
+        <v>-5718547</v>
       </c>
       <c r="G127">
-        <v>-94565700.45483218</v>
+        <v>5865149.842673674</v>
       </c>
       <c r="H127">
-        <v>130446013.03068407</v>
+        <v>-127504948.92741339</v>
       </c>
       <c r="I127">
-        <v>86218578.93837053</v>
+        <v>-101197972.68062083</v>
+      </c>
+      <c r="J127">
+        <v>139594715.6260981</v>
+      </c>
+      <c r="K127">
+        <v>92265434.02102329</v>
       </c>
     </row>
     <row r="128">
@@ -5133,16 +5844,22 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>59482591</v>
+        <v>63653574</v>
       </c>
       <c r="C128">
-        <v>77375192.0914661</v>
-      </c>
-      <c r="E128">
-        <v>77375181</v>
+        <v>63654343.91157151</v>
+      </c>
+      <c r="D128">
+        <v>82801824.95100275</v>
       </c>
       <c r="F128">
-        <v>262944002.57942382</v>
+        <v>82800812</v>
+      </c>
+      <c r="G128">
+        <v>82801813.0816476</v>
+      </c>
+      <c r="H128">
+        <v>281385321.1215327</v>
       </c>
     </row>
     <row r="129">
@@ -5150,28 +5867,34 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>697646099</v>
+        <v>429861163</v>
       </c>
       <c r="C129">
-        <v>59482592.692757554</v>
-      </c>
-      <c r="E129">
-        <v>75654360</v>
+        <v>746574820.7624693</v>
+      </c>
+      <c r="D129">
+        <v>63654345.72304895</v>
       </c>
       <c r="F129">
-        <v>77375192.0914661</v>
+        <v>77082265</v>
+      </c>
+      <c r="G129">
+        <v>80960303.99633801</v>
+      </c>
+      <c r="H129">
+        <v>82801824.95100275</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5182,6 +5905,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5189,27 +5914,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5223,16 +5954,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-36442646</v>
+        <v>-5171112.929739259</v>
       </c>
       <c r="C3">
-        <v>-88179163.77521276</v>
+        <v>-38998515.07026074</v>
+      </c>
+      <c r="D3">
+        <v>-94363522.54363269</v>
       </c>
       <c r="E3">
-        <v>24199355</v>
+        <v>241833242.0440809</v>
       </c>
       <c r="F3">
-        <v>54631925.47460137</v>
+        <v>100958936.08070622</v>
+      </c>
+      <c r="G3">
+        <v>25896552.919293776</v>
+      </c>
+      <c r="H3">
+        <v>58463481.73891114</v>
       </c>
     </row>
     <row r="4">
@@ -5240,16 +5980,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>4586945</v>
+        <v>87457304.13194318</v>
       </c>
       <c r="C4">
-        <v>227198848.83638382</v>
+        <v>4908645.868056813</v>
+      </c>
+      <c r="D4">
+        <v>243133216.24043447</v>
       </c>
       <c r="E4">
-        <v>44350086</v>
+        <v>179997968.4205547</v>
       </c>
       <c r="F4">
-        <v>127144376.50850388</v>
+        <v>112230486.41654208</v>
+      </c>
+      <c r="G4">
+        <v>47460535.58345791</v>
+      </c>
+      <c r="H4">
+        <v>136061522.07953823</v>
       </c>
     </row>
     <row r="5">
@@ -5257,16 +6006,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>13646490</v>
+        <v>-22878204.130259603</v>
       </c>
       <c r="C5">
-        <v>27892500.657923535</v>
+        <v>14603573.130259601</v>
+      </c>
+      <c r="D5">
+        <v>29848713.70907834</v>
       </c>
       <c r="E5">
-        <v>21511056</v>
+        <v>-166923984.56344405</v>
       </c>
       <c r="F5">
-        <v>-54953534.31236857</v>
+        <v>-22598123.71771053</v>
+      </c>
+      <c r="G5">
+        <v>23019712.71771053</v>
+      </c>
+      <c r="H5">
+        <v>-58807646.29563388</v>
       </c>
     </row>
     <row r="6">
@@ -5274,16 +6032,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>28565000</v>
+        <v>47233529.87010246</v>
       </c>
       <c r="C6">
-        <v>41425869.360058054</v>
+        <v>30568378.129897542</v>
+      </c>
+      <c r="D6">
+        <v>44331231.89070511</v>
       </c>
       <c r="E6">
-        <v>35646699</v>
+        <v>49017657.50186208</v>
       </c>
       <c r="F6">
-        <v>46542483.92780057</v>
+        <v>24617560.888337456</v>
+      </c>
+      <c r="G6">
+        <v>38146745.111662544</v>
+      </c>
+      <c r="H6">
+        <v>49806695.17975448</v>
       </c>
     </row>
     <row r="7">
@@ -5291,16 +6058,25 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>6755364</v>
+        <v>-3319838.798077969</v>
       </c>
       <c r="C7">
-        <v>1756740.9290547995</v>
+        <v>7229144.798077969</v>
+      </c>
+      <c r="D7">
+        <v>1879948.223196731</v>
       </c>
       <c r="E7">
-        <v>837001</v>
+        <v>3548701.2637279425</v>
       </c>
       <c r="F7">
-        <v>976868.9211172387</v>
+        <v>493580.75956231856</v>
+      </c>
+      <c r="G7">
+        <v>895703.2404376814</v>
+      </c>
+      <c r="H7">
+        <v>1045380.6603905745</v>
       </c>
     </row>
     <row r="8">
@@ -5308,16 +6084,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>7359269</v>
+        <v>-5333385.080225204</v>
       </c>
       <c r="C8">
-        <v>-950143.2743246797</v>
+        <v>7875404.080225204</v>
+      </c>
+      <c r="D8">
+        <v>-1016780.6366930082</v>
       </c>
       <c r="E8">
-        <v>9209263</v>
+        <v>8087422.586133372</v>
       </c>
       <c r="F8">
-        <v>-780059.1414245395</v>
+        <v>-1028540.5866155997</v>
+      </c>
+      <c r="G8">
+        <v>9855145.5866156</v>
+      </c>
+      <c r="H8">
+        <v>-834767.8207158614</v>
       </c>
     </row>
     <row r="9">
@@ -5340,16 +6125,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>438724</v>
+        <v>2958673.5245348793</v>
       </c>
       <c r="C12">
-        <v>9058015.713993412</v>
+        <v>469493.4754651206</v>
+      </c>
+      <c r="D12">
+        <v>9693290.721228935</v>
       </c>
       <c r="E12">
-        <v>-31359018</v>
+        <v>3690952.989807613</v>
       </c>
       <c r="F12">
-        <v>-47335811.070660084</v>
+        <v>6596104.829380825</v>
+      </c>
+      <c r="G12">
+        <v>-33558351.829380825</v>
+      </c>
+      <c r="H12">
+        <v>-50655661.540112995</v>
       </c>
     </row>
     <row r="13">
@@ -5392,16 +6186,25 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>42490621</v>
+        <v>-86351870.83781429</v>
       </c>
       <c r="C20">
-        <v>-2540933.5413606465</v>
+        <v>45470658.83781429</v>
+      </c>
+      <c r="D20">
+        <v>-2719139.4117014706</v>
       </c>
       <c r="E20">
-        <v>30090094</v>
+        <v>-157283290.06208387</v>
       </c>
       <c r="F20">
-        <v>17084799.273143888</v>
+        <v>-62736455.09491199</v>
+      </c>
+      <c r="G20">
+        <v>32200433.094911996</v>
+      </c>
+      <c r="H20">
+        <v>18283024.836508352</v>
       </c>
     </row>
     <row r="21">
@@ -5444,10 +6247,16 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-28504960</v>
-      </c>
-      <c r="E28">
-        <v>-51154061</v>
+        <v>-80593351.71634503</v>
+      </c>
+      <c r="C28">
+        <v>-30504127.28365497</v>
+      </c>
+      <c r="F28">
+        <v>2987693.6661244407</v>
+      </c>
+      <c r="G28">
+        <v>-54741700.66612444</v>
       </c>
     </row>
     <row r="29">
@@ -5465,16 +6274,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-90409013</v>
+        <v>-90192721.9532707</v>
       </c>
       <c r="C31">
-        <v>64725071.554199874</v>
+        <v>-96749760.0467293</v>
+      </c>
+      <c r="D31">
+        <v>69264500.67402267</v>
       </c>
       <c r="E31">
-        <v>-280057527</v>
+        <v>-203295279.95061517</v>
       </c>
       <c r="F31">
-        <v>-714297489.288287</v>
+        <v>-15863485.284614384</v>
+      </c>
+      <c r="G31">
+        <v>-299699085.7153856</v>
+      </c>
+      <c r="H31">
+        <v>-764394039.9020059</v>
       </c>
     </row>
     <row r="32">
@@ -5487,16 +6305,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>119519209</v>
+        <v>-54664590.960905075</v>
       </c>
       <c r="C33">
-        <v>274802101.556134</v>
+        <v>127901570.96090508</v>
+      </c>
+      <c r="D33">
+        <v>294075076.18618625</v>
       </c>
       <c r="E33">
-        <v>-50835655</v>
+        <v>-241917753.84025997</v>
       </c>
       <c r="F33">
-        <v>-40342245.95438037</v>
+        <v>-55671794.42496004</v>
+      </c>
+      <c r="G33">
+        <v>-54400963.57503996</v>
+      </c>
+      <c r="H33">
+        <v>-43171609.625164665</v>
       </c>
     </row>
     <row r="34">
@@ -5519,16 +6346,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-96474000</v>
+        <v>37140229.93414092</v>
       </c>
       <c r="C37">
-        <v>-149167669.3539394</v>
+        <v>-103240108.93414092</v>
+      </c>
+      <c r="D37">
+        <v>-159629396.8691318</v>
       </c>
       <c r="E37">
-        <v>107803364</v>
+        <v>-9534856.841213226</v>
       </c>
       <c r="F37">
-        <v>-145785183.10021725</v>
+        <v>-17616135.715455413</v>
+      </c>
+      <c r="G37">
+        <v>115364046.71545541</v>
+      </c>
+      <c r="H37">
+        <v>-156009683.27476946</v>
       </c>
     </row>
     <row r="38">
@@ -5541,16 +6377,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-26379485</v>
+        <v>73860933.18876109</v>
       </c>
       <c r="C39">
-        <v>42702145.320696704</v>
+        <v>-28229584.188761078</v>
+      </c>
+      <c r="D39">
+        <v>45697018.20832809</v>
       </c>
       <c r="E39">
-        <v>-27500122</v>
+        <v>29982916.701822273</v>
       </c>
       <c r="F39">
-        <v>-284802242.4531461</v>
+        <v>39324383.960592136</v>
+      </c>
+      <c r="G39">
+        <v>-29428815.960592132</v>
+      </c>
+      <c r="H39">
+        <v>-304776567.1118686</v>
       </c>
     </row>
     <row r="40">
@@ -5558,16 +6403,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>55422338</v>
+        <v>27713107.932015076</v>
       </c>
       <c r="C40">
-        <v>181188112.3780372</v>
+        <v>59309329.06798492</v>
+      </c>
+      <c r="D40">
+        <v>193895562.11497325</v>
       </c>
       <c r="E40">
-        <v>159352655</v>
+        <v>-145325727.51906615</v>
       </c>
       <c r="F40">
-        <v>-83834554.39180163</v>
+        <v>63767081.55179039</v>
+      </c>
+      <c r="G40">
+        <v>170528696.4482096</v>
+      </c>
+      <c r="H40">
+        <v>-89714208.26186085</v>
       </c>
     </row>
     <row r="41">
@@ -5580,16 +6434,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>19536665</v>
+        <v>-7023116.7502935305</v>
       </c>
       <c r="C42">
-        <v>3604185.2204305883</v>
+        <v>20906849.75029353</v>
+      </c>
+      <c r="D42">
+        <v>3856961.1996607874</v>
       </c>
       <c r="E42">
-        <v>11072667</v>
+        <v>1192182.316385625</v>
       </c>
       <c r="F42">
-        <v>-6283425.45720888</v>
+        <v>-2370706.59014312</v>
+      </c>
+      <c r="G42">
+        <v>11849237.59014312</v>
+      </c>
+      <c r="H42">
+        <v>-6724107.310589371</v>
       </c>
     </row>
     <row r="43">
@@ -5602,16 +6465,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>22086197</v>
+        <v>2245503.3349410594</v>
       </c>
       <c r="C44">
-        <v>-11983580.813216452</v>
+        <v>23635190.66505894</v>
+      </c>
+      <c r="D44">
+        <v>-12824037.446125876</v>
       </c>
       <c r="E44">
-        <v>32048629</v>
+        <v>16047185.818740688</v>
       </c>
       <c r="F44">
-        <v>-22362815.627536565</v>
+        <v>-12091965.017391913</v>
+      </c>
+      <c r="G44">
+        <v>34296328.01739191</v>
+      </c>
+      <c r="H44">
+        <v>-23931209.667485375</v>
       </c>
     </row>
     <row r="45">
@@ -5629,16 +6501,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-4179610</v>
+        <v>-16563399.170820897</v>
       </c>
       <c r="C47">
-        <v>-3434783.180650302</v>
+        <v>-4472742.829179103</v>
+      </c>
+      <c r="D47">
+        <v>-3675678.314732386</v>
       </c>
       <c r="E47">
-        <v>-6312708</v>
+        <v>4886133.1919446895</v>
       </c>
       <c r="F47">
-        <v>28525868.910493664</v>
+        <v>-2139682.4443329517</v>
+      </c>
+      <c r="G47">
+        <v>-6755443.555667048</v>
+      </c>
+      <c r="H47">
+        <v>30526502.619984552</v>
       </c>
     </row>
     <row r="48">
@@ -5646,16 +6527,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-27627261</v>
+        <v>12378782.72908704</v>
       </c>
       <c r="C48">
-        <v>-21345913.74061244</v>
+        <v>-29564871.72908704</v>
+      </c>
+      <c r="D48">
+        <v>-22842988.368675537</v>
       </c>
       <c r="E48">
-        <v>3274636</v>
+        <v>-5597211.095684273</v>
       </c>
       <c r="F48">
-        <v>-18642452.191731375</v>
+        <v>5649997.630639764</v>
+      </c>
+      <c r="G48">
+        <v>3504299.369360237</v>
+      </c>
+      <c r="H48">
+        <v>-19949922.207785115</v>
       </c>
     </row>
     <row r="49">
@@ -5663,10 +6553,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-10271525</v>
-      </c>
-      <c r="E49">
-        <v>14707081</v>
+        <v>-16014251.714661445</v>
+      </c>
+      <c r="C49">
+        <v>-10991908.285338555</v>
+      </c>
+      <c r="F49">
+        <v>92620056.364956</v>
+      </c>
+      <c r="G49">
+        <v>15738547.635043994</v>
       </c>
     </row>
     <row r="50">
@@ -5694,16 +6590,25 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-26171121</v>
+        <v>10843138.784922186</v>
       </c>
       <c r="C54">
-        <v>57771930.465589985</v>
+        <v>-28006606.784922186</v>
+      </c>
+      <c r="D54">
+        <v>61823707.88609496</v>
       </c>
       <c r="E54">
-        <v>9492274</v>
+        <v>-54664508.35883014</v>
       </c>
       <c r="F54">
-        <v>-15351613.661704447</v>
+        <v>8338879.715750217</v>
+      </c>
+      <c r="G54">
+        <v>10158005.284249783</v>
+      </c>
+      <c r="H54">
+        <v>-16428283.959918868</v>
       </c>
     </row>
     <row r="55">
@@ -5767,16 +6672,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-100268926</v>
+        <v>-229537392.66999072</v>
       </c>
       <c r="C67">
-        <v>-398408726.50887275</v>
+        <v>-107301188.33000927</v>
+      </c>
+      <c r="D67">
+        <v>-426350729.99034333</v>
       </c>
       <c r="E67">
-        <v>-85654993</v>
+        <v>-549729400.7281468</v>
       </c>
       <c r="F67">
-        <v>-168955580.10956928</v>
+        <v>-289944252.4618335</v>
+      </c>
+      <c r="G67">
+        <v>-91662321.53816652</v>
+      </c>
+      <c r="H67">
+        <v>-180805113.24857378</v>
       </c>
     </row>
     <row r="68">
@@ -5829,16 +6743,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>3805030</v>
+        <v>-1074420.029952881</v>
       </c>
       <c r="C77">
-        <v>-4078608.4824336097</v>
+        <v>4071892.029952881</v>
+      </c>
+      <c r="D77">
+        <v>-4364657.669695016</v>
       </c>
       <c r="E77">
-        <v>2550135</v>
+        <v>9196584.90195176</v>
       </c>
       <c r="F77">
-        <v>17078155.9464295</v>
+        <v>-1042495.2055762741</v>
+      </c>
+      <c r="G77">
+        <v>2728986.205576274</v>
+      </c>
+      <c r="H77">
+        <v>18275915.586620517</v>
       </c>
     </row>
     <row r="78">
@@ -5846,16 +6769,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-104073956</v>
+        <v>-228462972.64003783</v>
       </c>
       <c r="C78">
-        <v>-405813596.97940326</v>
+        <v>-111373080.35996215</v>
+      </c>
+      <c r="D78">
+        <v>-434274933.7553035</v>
       </c>
       <c r="E78">
-        <v>-88205128</v>
+        <v>-546637124.1954433</v>
       </c>
       <c r="F78">
-        <v>-186033736.0559988</v>
+        <v>-288901757.2562572</v>
+      </c>
+      <c r="G78">
+        <v>-94391307.74374281</v>
+      </c>
+      <c r="H78">
+        <v>-199081028.8351943</v>
       </c>
     </row>
     <row r="79">
@@ -5969,16 +6901,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>794861788</v>
+        <v>-78362504.32383883</v>
       </c>
       <c r="C101">
-        <v>454682892.6350937</v>
+        <v>850608636.3238388</v>
+      </c>
+      <c r="D101">
+        <v>486571629.3108753</v>
       </c>
       <c r="E101">
-        <v>66936400</v>
+        <v>336063353.46870124</v>
       </c>
       <c r="F101">
-        <v>19532635.285605848</v>
+        <v>189531458.53845358</v>
+      </c>
+      <c r="G101">
+        <v>71630918.46154644</v>
+      </c>
+      <c r="H101">
+        <v>20902537.41585082</v>
       </c>
     </row>
     <row r="102">
@@ -5996,9 +6937,12 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>912520327</v>
-      </c>
-      <c r="E104">
+        <v>-11800.027612566948</v>
+      </c>
+      <c r="C104">
+        <v>976519041.0276126</v>
+      </c>
+      <c r="G104">
         <v>0</v>
       </c>
     </row>
@@ -6029,8 +6973,14 @@
       <c r="B109">
         <v>0</v>
       </c>
-      <c r="E109">
-        <v>66936400</v>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>189531458.53845358</v>
+      </c>
+      <c r="G109">
+        <v>71630918.46154644</v>
       </c>
     </row>
     <row r="110">
@@ -6038,9 +6988,12 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-117658539</v>
-      </c>
-      <c r="E110">
+        <v>-78350704.29622626</v>
+      </c>
+      <c r="C110">
+        <v>-125910404.70377374</v>
+      </c>
+      <c r="G110">
         <v>0</v>
       </c>
     </row>
@@ -6119,16 +7072,25 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>658150216</v>
+        <v>-313071009.92356884</v>
       </c>
       <c r="C125">
-        <v>-31904997.648991723</v>
+        <v>704308932.9235688</v>
+      </c>
+      <c r="D125">
+        <v>-34142623.223100685</v>
       </c>
       <c r="E125">
-        <v>5480762</v>
+        <v>28167194.784635402</v>
       </c>
       <c r="F125">
-        <v>-143506141.89579502</v>
+        <v>546142.1573263258</v>
+      </c>
+      <c r="G125">
+        <v>5865149.842673674</v>
+      </c>
+      <c r="H125">
+        <v>-153570803.761015</v>
       </c>
     </row>
     <row r="126">
@@ -6136,9 +7098,15 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
+        <v>-25030334</v>
+      </c>
+      <c r="C126">
         <v>0</v>
       </c>
-      <c r="E126">
+      <c r="F126">
+        <v>-12129839</v>
+      </c>
+      <c r="G126">
         <v>0</v>
       </c>
     </row>
@@ -6147,16 +7115,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>658150216</v>
+        <v>-338101343.92356884</v>
       </c>
       <c r="C127">
-        <v>-12571276.978729606</v>
+        <v>704308932.9235688</v>
+      </c>
+      <c r="D127">
+        <v>-13452951.103150098</v>
       </c>
       <c r="E127">
-        <v>5480762</v>
+        <v>19607361.664684817</v>
       </c>
       <c r="F127">
-        <v>-24582880.16774635</v>
+        <v>-11583696.842673674</v>
+      </c>
+      <c r="G127">
+        <v>5865149.842673674</v>
+      </c>
+      <c r="H127">
+        <v>-26306976.246792555</v>
       </c>
     </row>
     <row r="128">
@@ -6164,10 +7141,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>59482591</v>
-      </c>
-      <c r="E128">
-        <v>77375181</v>
+        <v>-769.9115715101361</v>
+      </c>
+      <c r="C128">
+        <v>63654343.91157151</v>
+      </c>
+      <c r="F128">
+        <v>-1001.0816476047039</v>
+      </c>
+      <c r="G128">
+        <v>82801813.0816476</v>
       </c>
     </row>
     <row r="129">
@@ -6175,22 +7158,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>697646099</v>
-      </c>
-      <c r="E129">
-        <v>75654360</v>
+        <v>-316713657.7624693</v>
+      </c>
+      <c r="C129">
+        <v>746574820.7624693</v>
+      </c>
+      <c r="F129">
+        <v>-3878038.99633801</v>
+      </c>
+      <c r="G129">
+        <v>80960303.99633801</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6201,6 +7190,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6208,27 +7199,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6242,22 +7239,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>195704591.79326212</v>
+        <v>103300091.50044823</v>
       </c>
       <c r="C3">
-        <v>256346592.79326212</v>
+        <v>209430140.51089373</v>
       </c>
       <c r="D3">
-        <v>399157682.0430763</v>
-      </c>
-      <c r="F3">
-        <v>-111615397.24178185</v>
+        <v>274325208.5004482</v>
+      </c>
+      <c r="E3">
+        <v>427152212.78299206</v>
       </c>
       <c r="H3">
-        <v>500959246.4959997</v>
-      </c>
-      <c r="I3">
-        <v>-455990857.00111663</v>
+        <v>-119443433.15265222</v>
+      </c>
+      <c r="J3">
+        <v>536093529.6537115</v>
+      </c>
+      <c r="K3">
+        <v>-487971326.4689715</v>
       </c>
     </row>
     <row r="4">
@@ -6265,22 +7265,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>504862297.1742352</v>
+        <v>515497134.66098917</v>
       </c>
       <c r="C4">
-        <v>544625438.1742352</v>
+        <v>540270316.9455881</v>
       </c>
       <c r="D4">
-        <v>444570965.8463553</v>
-      </c>
-      <c r="F4">
-        <v>249753005.87327364</v>
+        <v>582822206.6609892</v>
+      </c>
+      <c r="E4">
+        <v>475750512.5000929</v>
       </c>
       <c r="H4">
-        <v>303938292.47553766</v>
-      </c>
-      <c r="I4">
-        <v>306406070.28391963</v>
+        <v>267269186.85848942</v>
+      </c>
+      <c r="J4">
+        <v>325254705.14782524</v>
+      </c>
+      <c r="K4">
+        <v>327895558.1212959</v>
       </c>
     </row>
     <row r="5">
@@ -6288,22 +7291,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-135562293.5530398</v>
+        <v>-145349901.8543657</v>
       </c>
       <c r="C5">
-        <v>-127697727.5530398</v>
+        <v>-145069821.44181663</v>
       </c>
       <c r="D5">
-        <v>-210543762.5233319</v>
-      </c>
-      <c r="F5">
-        <v>63179111.70837851</v>
+        <v>-136653681.8543657</v>
+      </c>
+      <c r="E5">
+        <v>-225310041.85907793</v>
       </c>
       <c r="H5">
-        <v>-54297633.25210114</v>
-      </c>
-      <c r="I5">
-        <v>-233478545.67667097</v>
+        <v>67610116.45764926</v>
+      </c>
+      <c r="J5">
+        <v>-58105744.26076408</v>
+      </c>
+      <c r="K5">
+        <v>-249853333.43122816</v>
       </c>
     </row>
     <row r="6">
@@ -6311,22 +7317,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>138800212.28227282</v>
+        <v>171150797.3925672</v>
       </c>
       <c r="C6">
-        <v>145881911.28227282</v>
+        <v>148534828.4108022</v>
       </c>
       <c r="D6">
-        <v>150998525.85001534</v>
-      </c>
-      <c r="F6">
-        <v>103724450.1488672</v>
+        <v>156113195.3925672</v>
+      </c>
+      <c r="E6">
+        <v>161588658.68161654</v>
       </c>
       <c r="H6">
-        <v>107375616.53973901</v>
-      </c>
-      <c r="I6">
-        <v>64584697.911915466</v>
+        <v>110999062.26032837</v>
+      </c>
+      <c r="J6">
+        <v>114906299.60852872</v>
+      </c>
+      <c r="K6">
+        <v>69114282.06464681</v>
       </c>
     </row>
     <row r="7">
@@ -6334,22 +7343,25 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>12289465.491156474</v>
+        <v>9337955.486924674</v>
       </c>
       <c r="C7">
-        <v>6371102.491156474</v>
+        <v>13151375.04456496</v>
       </c>
       <c r="D7">
-        <v>5591230.483218913</v>
-      </c>
-      <c r="F7">
-        <v>18021320.166625403</v>
+        <v>6817933.486924673</v>
+      </c>
+      <c r="E7">
+        <v>5983365.924118517</v>
       </c>
       <c r="H7">
-        <v>2217751.466182786</v>
-      </c>
-      <c r="I7">
-        <v>12069913.811090454</v>
+        <v>19285227.700099893</v>
+      </c>
+      <c r="J7">
+        <v>2373291.2801123783</v>
+      </c>
+      <c r="K7">
+        <v>12916425.323741842</v>
       </c>
     </row>
     <row r="8">
@@ -6357,22 +7369,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>13005385.542253982</v>
+        <v>9612660.949440364</v>
       </c>
       <c r="C8">
-        <v>14855379.542253982</v>
+        <v>13917505.443049967</v>
       </c>
       <c r="D8">
-        <v>15025463.675154123</v>
-      </c>
-      <c r="F8">
-        <v>7842196.195619076</v>
+        <v>15897246.949440364</v>
+      </c>
+      <c r="E8">
+        <v>16079259.76541751</v>
       </c>
       <c r="H8">
-        <v>4186059.950897179</v>
-      </c>
-      <c r="I8">
-        <v>9714401.937996328</v>
+        <v>8392200.898880722</v>
+      </c>
+      <c r="J8">
+        <v>4479645.141027316</v>
+      </c>
+      <c r="K8">
+        <v>10395711.946314763</v>
       </c>
     </row>
     <row r="9">
@@ -6395,22 +7410,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>19109608.4555547</v>
+        <v>16812410.711036548</v>
       </c>
       <c r="C12">
-        <v>-12688133.544445299</v>
+        <v>20449842.015882492</v>
       </c>
       <c r="D12">
-        <v>-69081960.32909879</v>
-      </c>
-      <c r="F12">
-        <v>18937511.751026645</v>
+        <v>-13578003.288963452</v>
+      </c>
+      <c r="E12">
+        <v>-73926955.55030538</v>
       </c>
       <c r="H12">
-        <v>-11963242.626748476</v>
-      </c>
-      <c r="I12">
-        <v>-4774000.2931142</v>
+        <v>20265675.478549294</v>
+      </c>
+      <c r="J12">
+        <v>-12802272.860989187</v>
+      </c>
+      <c r="K12">
+        <v>-5108820.099847945</v>
       </c>
     </row>
     <row r="13">
@@ -6453,22 +7471,25 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>-165650491.71025962</v>
+        <v>-200883641.47378534</v>
       </c>
       <c r="C20">
-        <v>-178051018.71025962</v>
+        <v>-177268225.73088306</v>
       </c>
       <c r="D20">
-        <v>-158425285.89575508</v>
-      </c>
-      <c r="F20">
-        <v>-826813.1053226215</v>
+        <v>-190538451.47378534</v>
+      </c>
+      <c r="E20">
+        <v>-169536287.2255755</v>
       </c>
       <c r="H20">
-        <v>45040931.77977679</v>
-      </c>
-      <c r="I20">
-        <v>-7724343.744145022</v>
+        <v>-884800.8278052405</v>
+      </c>
+      <c r="J20">
+        <v>48199833.151308805</v>
+      </c>
+      <c r="K20">
+        <v>-8266082.98184259</v>
       </c>
     </row>
     <row r="21">
@@ -6480,8 +7501,8 @@
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="H22">
-        <v>53728454.617797464</v>
+      <c r="J22">
+        <v>57496646.84375539</v>
       </c>
     </row>
     <row r="23">
@@ -6514,13 +7535,16 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-161906663.1571259</v>
+        <v>-256842872.83344007</v>
       </c>
       <c r="C28">
-        <v>-184555764.1571259</v>
-      </c>
-      <c r="F28">
-        <v>-390152316.32895356</v>
+        <v>-173261827.4509706</v>
+      </c>
+      <c r="D28">
+        <v>-197499400.83344007</v>
+      </c>
+      <c r="H28">
+        <v>-417515264.61749876</v>
       </c>
     </row>
     <row r="29">
@@ -6538,22 +7562,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-230479567.2504105</v>
+        <v>-320973261.2765925</v>
       </c>
       <c r="C31">
-        <v>-420128081.2504105</v>
+        <v>-246644024.60793617</v>
       </c>
       <c r="D31">
-        <v>-1199150642.0928974</v>
-      </c>
-      <c r="F31">
-        <v>-216910242.07974115</v>
+        <v>-449593350.2765925</v>
+      </c>
+      <c r="E31">
+        <v>-1283251890.852621</v>
       </c>
       <c r="H31">
-        <v>-226714300.0089985</v>
-      </c>
-      <c r="I31">
-        <v>-342975297.432422</v>
+        <v>-232123028.18628183</v>
+      </c>
+      <c r="J31">
+        <v>-242614684.05846664</v>
+      </c>
+      <c r="K31">
+        <v>-367029531.9841888</v>
       </c>
     </row>
     <row r="32">
@@ -6566,22 +7593,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>116235066.9853011</v>
+        <v>125394302.34592628</v>
       </c>
       <c r="C33">
-        <v>-54119797.01469889</v>
+        <v>124387098.88187131</v>
       </c>
       <c r="D33">
-        <v>-369264144.5252133</v>
-      </c>
-      <c r="F33">
-        <v>-87863748.13809276</v>
+        <v>-57915435.65407372</v>
+      </c>
+      <c r="E33">
+        <v>-395162121.46542466</v>
       </c>
       <c r="H33">
-        <v>-328113883.0962218</v>
-      </c>
-      <c r="I33">
-        <v>-216076531.05030856</v>
+        <v>-94025985.54158238</v>
+      </c>
+      <c r="J33">
+        <v>-351125826.99647486</v>
+      </c>
+      <c r="K33">
+        <v>-231230845.6552557</v>
       </c>
     </row>
     <row r="34">
@@ -6604,22 +7634,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-271013251.02848995</v>
+        <v>-235264132.71034503</v>
       </c>
       <c r="C37">
-        <v>-66735887.028489955</v>
+        <v>-290020498.35994136</v>
       </c>
       <c r="D37">
-        <v>-63353400.774767786</v>
-      </c>
-      <c r="F37">
-        <v>-16874056.459777966</v>
+        <v>-71416342.71034501</v>
+      </c>
+      <c r="E37">
+        <v>-67796629.11598268</v>
       </c>
       <c r="H37">
-        <v>17155434.476196982</v>
-      </c>
-      <c r="I37">
-        <v>-109445314.95682493</v>
+        <v>-18057501.783571962</v>
+      </c>
+      <c r="J37">
+        <v>18358613.969930686</v>
+      </c>
+      <c r="K37">
+        <v>-117121154.28482252</v>
       </c>
     </row>
     <row r="38">
@@ -6632,22 +7665,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>81087726.8547812</v>
+        <v>121311283.91015036</v>
       </c>
       <c r="C39">
-        <v>79967089.8547812</v>
+        <v>86774734.68198141</v>
       </c>
       <c r="D39">
-        <v>-247537297.9190616</v>
-      </c>
-      <c r="F39">
-        <v>-152833767.0080965</v>
+        <v>85575502.91015036</v>
+      </c>
+      <c r="E39">
+        <v>-264898082.41004634</v>
       </c>
       <c r="H39">
-        <v>-5131640.613277422</v>
-      </c>
-      <c r="I39">
-        <v>-3514919.5069701415</v>
+        <v>-163552612.6700561</v>
+      </c>
+      <c r="J39">
+        <v>-5491543.171482708</v>
+      </c>
+      <c r="K39">
+        <v>-3761434.923340323</v>
       </c>
     </row>
     <row r="40">
@@ -6655,22 +7691,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>160396962.3036851</v>
+        <v>135592271.5959071</v>
       </c>
       <c r="C40">
-        <v>264327279.3036851</v>
+        <v>171646245.2156824</v>
       </c>
       <c r="D40">
-        <v>-695387.4661537558</v>
-      </c>
-      <c r="F40">
-        <v>65599493.29057136</v>
+        <v>282865612.5959071</v>
+      </c>
+      <c r="E40">
+        <v>-744157.7809270024</v>
       </c>
       <c r="H40">
-        <v>133920061.68771271</v>
-      </c>
-      <c r="I40">
-        <v>2211190.954656957</v>
+        <v>70200249.11730656</v>
+      </c>
+      <c r="J40">
+        <v>143312413.26270634</v>
+      </c>
+      <c r="K40">
+        <v>2366270.653574759</v>
       </c>
     </row>
     <row r="41">
@@ -6683,22 +7722,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>22039563.598784246</v>
+        <v>18932876.516046412</v>
       </c>
       <c r="C42">
-        <v>13575565.598784246</v>
+        <v>23585286.67619682</v>
       </c>
       <c r="D42">
-        <v>3687954.921144777</v>
-      </c>
-      <c r="F42">
-        <v>524889.2092934571</v>
+        <v>14527674.516046412</v>
+      </c>
+      <c r="E42">
+        <v>3946606.0057962537</v>
       </c>
       <c r="H42">
-        <v>2679766.274897393</v>
-      </c>
-      <c r="I42">
-        <v>5207655.502206568</v>
+        <v>561701.7968137695</v>
+      </c>
+      <c r="J42">
+        <v>2867709.042212864</v>
+      </c>
+      <c r="K42">
+        <v>5572889.289749408</v>
       </c>
     </row>
     <row r="43">
@@ -6711,22 +7753,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>13798621.310458269</v>
+        <v>29103842.372614812</v>
       </c>
       <c r="C44">
-        <v>23761053.31045827</v>
+        <v>14766374.02028184</v>
       </c>
       <c r="D44">
-        <v>13381818.496138155</v>
-      </c>
-      <c r="F44">
-        <v>885489.8094351812</v>
+        <v>25427511.372614812</v>
+      </c>
+      <c r="E44">
+        <v>14320339.151255313</v>
       </c>
       <c r="H44">
-        <v>13242287.441052264</v>
-      </c>
-      <c r="I44">
-        <v>3584920.4979716204</v>
+        <v>947592.7647465616</v>
+      </c>
+      <c r="J44">
+        <v>14171022.223100958</v>
+      </c>
+      <c r="K44">
+        <v>3836345.3648736943</v>
       </c>
     </row>
     <row r="45">
@@ -6744,22 +7789,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-5047938.222780012</v>
+        <v>-19825687.122787695</v>
       </c>
       <c r="C47">
-        <v>-7181036.222780012</v>
+        <v>-5401970.396299751</v>
       </c>
       <c r="D47">
-        <v>24779615.868363954</v>
-      </c>
-      <c r="F47">
-        <v>38939403.42071278</v>
+        <v>-7684671.122787696</v>
+      </c>
+      <c r="E47">
+        <v>26517509.81192924</v>
       </c>
       <c r="H47">
-        <v>78836011.0882152</v>
-      </c>
-      <c r="I47">
-        <v>76178374.62560807</v>
+        <v>41670380.11261943</v>
+      </c>
+      <c r="J47">
+        <v>84365097.04874349</v>
+      </c>
+      <c r="K47">
+        <v>81521069.87140135</v>
       </c>
     </row>
     <row r="48">
@@ -6767,22 +7815,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-48923847.708455354</v>
+        <v>-45626288.46435981</v>
       </c>
       <c r="C48">
-        <v>-18021950.70845535</v>
+        <v>-52355073.56280709</v>
       </c>
       <c r="D48">
-        <v>-15318489.159574283</v>
-      </c>
-      <c r="F48">
-        <v>-21619778.373257976</v>
+        <v>-19285902.464359812</v>
+      </c>
+      <c r="E48">
+        <v>-16392836.303469388</v>
       </c>
       <c r="H48">
-        <v>31578164.987871297</v>
-      </c>
-      <c r="I48">
-        <v>32224083.118626047</v>
+        <v>-23136060.22749277</v>
+      </c>
+      <c r="J48">
+        <v>33792868.47532089</v>
+      </c>
+      <c r="K48">
+        <v>34484087.437752806</v>
       </c>
     </row>
     <row r="49">
@@ -6790,13 +7841,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>207393340.46406952</v>
+        <v>113304359.97318342</v>
       </c>
       <c r="C49">
-        <v>232371946.46406952</v>
-      </c>
-      <c r="F49">
-        <v>-77220198.74730141</v>
+        <v>221938668.05280086</v>
+      </c>
+      <c r="D49">
+        <v>248669123.97318342</v>
+      </c>
+      <c r="H49">
+        <v>-82635961.30136006</v>
       </c>
     </row>
     <row r="50">
@@ -6824,22 +7878,25 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-11688748.670807399</v>
+        <v>-10004268.472735185</v>
       </c>
       <c r="C54">
-        <v>23974646.3291926</v>
+        <v>-12508527.541907154</v>
       </c>
       <c r="D54">
-        <v>-49148897.79810183</v>
-      </c>
-      <c r="F54">
-        <v>-34395198.494480446</v>
+        <v>25656084.527264815</v>
+      </c>
+      <c r="E54">
+        <v>-52595907.31874901</v>
       </c>
       <c r="H54">
-        <v>-35310941.01910181</v>
-      </c>
-      <c r="I54">
-        <v>-10956428.609547343</v>
+        <v>-36807471.85129217</v>
+      </c>
+      <c r="J54">
+        <v>-37787439.0755965</v>
+      </c>
+      <c r="K54">
+        <v>-11724846.934705785</v>
       </c>
     </row>
     <row r="55">
@@ -6903,22 +7960,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-1283321109.9225612</v>
+        <v>-1312918711.7184901</v>
       </c>
       <c r="C67">
-        <v>-1268707176.9225612</v>
+        <v>-1373325571.5103328</v>
       </c>
       <c r="D67">
-        <v>-1039254030.5232577</v>
-      </c>
-      <c r="F67">
-        <v>-228133822.82834026</v>
+        <v>-1357686704.7184901</v>
+      </c>
+      <c r="E67">
+        <v>-1112141087.9767206</v>
       </c>
       <c r="H67">
-        <v>-68305830.84383556</v>
-      </c>
-      <c r="I67">
-        <v>-82218608.76390612</v>
+        <v>-244133763.7120867</v>
+      </c>
+      <c r="J67">
+        <v>-73096392.98831381</v>
+      </c>
+      <c r="K67">
+        <v>-87984929.87954456</v>
       </c>
     </row>
     <row r="68">
@@ -6971,22 +8031,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>7346111.747358326</v>
+        <v>7829399.232256744</v>
       </c>
       <c r="C77">
-        <v>6091216.747358326</v>
+        <v>7861324.056633351</v>
       </c>
       <c r="D77">
-        <v>27247981.176221434</v>
-      </c>
-      <c r="F77">
-        <v>20180991.959520414</v>
+        <v>6518418.232256744</v>
+      </c>
+      <c r="E77">
+        <v>29158991.488572277</v>
       </c>
       <c r="H77">
-        <v>9392636.006082168</v>
-      </c>
-      <c r="I77">
-        <v>3968821.23780448</v>
+        <v>21596365.94626438</v>
+      </c>
+      <c r="J77">
+        <v>10051379.277801868</v>
+      </c>
+      <c r="K77">
+        <v>4247170.604837226</v>
       </c>
     </row>
     <row r="78">
@@ -6994,22 +8057,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-1290667221.6699195</v>
+        <v>-1320748110.9507468</v>
       </c>
       <c r="C78">
-        <v>-1274798393.6699195</v>
+        <v>-1381186895.5669663</v>
       </c>
       <c r="D78">
-        <v>-1055018532.746515</v>
-      </c>
-      <c r="F78">
-        <v>-248314814.7878607</v>
+        <v>-1364205122.9507468</v>
+      </c>
+      <c r="E78">
+        <v>-1129011218.0306375</v>
       </c>
       <c r="H78">
-        <v>-137598348.6113114</v>
-      </c>
-      <c r="I78">
-        <v>-109059309.29529998</v>
+        <v>-265730129.6583511</v>
+      </c>
+      <c r="J78">
+        <v>-147248673.21547452</v>
+      </c>
+      <c r="K78">
+        <v>-116708076.49655801</v>
       </c>
     </row>
     <row r="79">
@@ -7111,11 +8177,11 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="H98">
-        <v>-59486476.519086964</v>
-      </c>
-      <c r="I98">
-        <v>-12847481.989605669</v>
+      <c r="J98">
+        <v>-63658501.93771124</v>
+      </c>
+      <c r="K98">
+        <v>-13748527.480319079</v>
       </c>
     </row>
     <row r="99">
@@ -7129,22 +8195,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>1740693270.2392063</v>
+        <v>1594881114.7795765</v>
       </c>
       <c r="C101">
-        <v>1012767882.2392063</v>
+        <v>1862775077.641869</v>
       </c>
       <c r="D101">
-        <v>577617624.8897185</v>
-      </c>
-      <c r="F101">
-        <v>220600639.4475436</v>
+        <v>1083797359.7795765</v>
+      </c>
+      <c r="E101">
+        <v>618128267.884552</v>
       </c>
       <c r="H101">
-        <v>-204287180.44864902</v>
-      </c>
-      <c r="I101">
-        <v>659854700.1465125</v>
+        <v>236072247.93732554</v>
+      </c>
+      <c r="J101">
+        <v>-218614660.5651992</v>
+      </c>
+      <c r="K101">
+        <v>706132959.3862683</v>
       </c>
     </row>
     <row r="102">
@@ -7171,16 +8240,16 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="H106">
-        <v>-163825756.72400376</v>
+      <c r="J106">
+        <v>-175315514.754278</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="H107">
-        <v>100359014.5319878</v>
+      <c r="J107">
+        <v>107397595.13242379</v>
       </c>
     </row>
     <row r="108">
@@ -7193,21 +8262,24 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>945831482.2392063</v>
+        <v>822634982.7795765</v>
       </c>
       <c r="C109">
-        <v>1012767882.2392063</v>
-      </c>
-      <c r="F109">
-        <v>220600639.4475436</v>
+        <v>1012166441.3180301</v>
+      </c>
+      <c r="D109">
+        <v>1083797359.7795765</v>
+      </c>
+      <c r="H109">
+        <v>236072247.93732554</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
-      <c r="H110">
-        <v>-140821177.79267764</v>
+      <c r="J110">
+        <v>-150697532.34602138</v>
       </c>
     </row>
     <row r="111">
@@ -7285,22 +8357,25 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>653076752.1099073</v>
+        <v>385262494.5615347</v>
       </c>
       <c r="C125">
-        <v>407298.10990731016</v>
+        <v>698879646.64243</v>
       </c>
       <c r="D125">
-        <v>-111193846.13689598</v>
-      </c>
-      <c r="F125">
-        <v>-119148580.62257853</v>
+        <v>435863.5615347182</v>
+      </c>
+      <c r="E125">
+        <v>-118992316.9763796</v>
       </c>
       <c r="H125">
-        <v>227952829.96120834</v>
-      </c>
-      <c r="I125">
-        <v>121645234.38148978</v>
+        <v>-127504948.92741339</v>
+      </c>
+      <c r="J125">
+        <v>243940077.0885508</v>
+      </c>
+      <c r="K125">
+        <v>130176703.03775224</v>
       </c>
     </row>
     <row r="126">
@@ -7313,22 +8388,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>653076752.1099073</v>
+        <v>372361999.5615347</v>
       </c>
       <c r="C127">
-        <v>407298.10990731016</v>
+        <v>698879646.64243</v>
       </c>
       <c r="D127">
-        <v>-11604305.079109434</v>
-      </c>
-      <c r="F127">
-        <v>-119148580.62257853</v>
+        <v>435863.5615347182</v>
+      </c>
+      <c r="E127">
+        <v>-12418161.58210774</v>
       </c>
       <c r="H127">
-        <v>130446013.03068407</v>
-      </c>
-      <c r="I127">
-        <v>86218578.93837053</v>
+        <v>-127504948.92741339</v>
+      </c>
+      <c r="J127">
+        <v>139594715.6260981</v>
+      </c>
+      <c r="K127">
+        <v>92265434.02102329</v>
       </c>
     </row>
     <row r="128">
@@ -7336,13 +8414,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>59482602.0914661</v>
+        <v>63654586.95100275</v>
       </c>
       <c r="C128">
-        <v>77375192.0914661</v>
-      </c>
-      <c r="F128">
-        <v>262944002.57942382</v>
+        <v>63654355.78092665</v>
+      </c>
+      <c r="D128">
+        <v>82801824.95100275</v>
+      </c>
+      <c r="H128">
+        <v>281385321.1215327</v>
       </c>
     </row>
     <row r="129">
@@ -7350,18 +8431,21 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>681474331.6927576</v>
+        <v>416433243.7230489</v>
       </c>
       <c r="C129">
-        <v>59482592.692757554</v>
-      </c>
-      <c r="F129">
-        <v>77375192.0914661</v>
+        <v>729268862.4891802</v>
+      </c>
+      <c r="D129">
+        <v>63654345.72304895</v>
+      </c>
+      <c r="H129">
+        <v>82801824.95100275</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>